--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -148,7 +148,7 @@
     <t xml:space="preserve">You work hard to build a better life. Your money should help you live it, not just keep you working for it.</t>
   </si>
   <si>
-    <t xml:space="preserve">Financial Freedom Without Quitting Your 9–5.  Know your money. Build your wealth. Reclaim your time.
+    <t xml:space="preserve">Build your options without quitting your 9–5.  Know your money. Build your wealth. Reclaim your time.
 — Liliane · iCyber · @cyber_cnslt · cybercnslt.com</t>
   </si>
   <si>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -145,7 +145,7 @@
     <t xml:space="preserve">Head to the How to Use tab. In about 20 minutes you'll have your first financial snapshot. You don't need everything figured out today. You just need somewhere meaningful to start.</t>
   </si>
   <si>
-    <t xml:space="preserve">You work hard to build a better life. Your money should help you live it, not just keep you working for it.</t>
+    <t xml:space="preserve">Financial freedom isn't about quitting your 9–5. It's about using your career as the engine to fuel your financial independence, build multiple income streams, and create the freedom to spend more time with the people you love.</t>
   </si>
   <si>
     <t xml:space="preserve">Build your options without quitting your 9–5.  Know your money. Build your wealth. Reclaim your time.
@@ -851,7 +851,7 @@
     <t xml:space="preserve">6 · Free to choose: extra income ≥ needs</t>
   </si>
   <si>
-    <t xml:space="preserve">Your money should help you live the life you work for, not just keep you working for it. Keep your first hour, and keep going. — Liliane</t>
+    <t xml:space="preserve">Your career is the engine. Keep your first hour, and keep going. — Liliane</t>
   </si>
   <si>
     <t xml:space="preserve">Educational tool. Not financial advice.</t>
@@ -1982,7 +1982,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="8" t="s">
         <v>23</v>
       </c>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -74,12 +74,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="293">
-  <si>
-    <t xml:space="preserve">Hey, I'm Liliane. 👋</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="294">
+  <si>
+    <t xml:space="preserve">Hey, I'm Liliane.</t>
   </si>
   <si>
     <t xml:space="preserve">You work hard for your money. But is it creating the life you're working so hard for?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and I'm also caring for my mum after her cerebral haemorrhage. I paid off €20,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I live it every week.</t>
   </si>
   <si>
     <t xml:space="preserve">You have a demanding career, bills to pay and people who depend on you. You earn a respectable income. Yet despite everything you do, you don't always feel as financially secure or independent as you thought you would.</t>
@@ -1009,6 +1012,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FF134E4E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color rgb="FF213534"/>
       <name val="Arial"/>
@@ -1035,14 +1046,6 @@
       <i val="true"/>
       <sz val="10.5"/>
       <color rgb="FF6E8180"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10.5"/>
-      <color rgb="FF134E4E"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1220,14 +1223,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F4F2"/>
-        <bgColor rgb="FFF2F8F7"/>
+        <fgColor rgb="FFF2F8F7"/>
+        <bgColor rgb="FFE8F4F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F8F7"/>
-        <bgColor rgb="FFE8F4F2"/>
+        <fgColor rgb="FFE8F4F2"/>
+        <bgColor rgb="FFF2F8F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1305,15 +1308,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1321,11 +1324,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1361,7 +1364,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1385,183 +1388,183 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1859,7 +1862,7 @@
     <tabColor rgb="FF9E1B5E"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B33"/>
+  <dimension ref="B2:B34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1882,119 +1885,124 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+    <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+    <row r="8" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+    <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
+    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7" t="s">
+    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="6" t="s">
+    <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5" t="s">
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="3" t="s">
+    <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="8" t="s">
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="9" t="s">
+    <row r="31" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="10" t="s">
+    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="9" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="10" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2029,7 +2037,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -2044,7 +2052,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -2059,42 +2067,42 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C6" s="21" t="n">
         <v>2500</v>
@@ -2127,12 +2135,12 @@
         <v>Level 1 · Stable</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C7" s="21" t="n">
         <v>2560</v>
@@ -2165,7 +2173,7 @@
         <v>Level 1 · Stable</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2413,160 +2421,160 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -2597,51 +2605,51 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="11"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2650,23 +2658,23 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2675,31 +2683,31 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2709,7 +2717,7 @@
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="14"/>
       <c r="C20" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2746,7 +2754,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -2755,7 +2763,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -2764,26 +2772,26 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>2500</v>
@@ -2791,10 +2799,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="22" t="n">
         <f aca="false">'Income Streams'!G23</f>
@@ -2803,10 +2811,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>0</v>
@@ -2829,7 +2837,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" s="23" t="n">
         <f aca="false">SUM(E7:E12)</f>
@@ -2838,52 +2846,52 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E16" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="19" t="s">
         <v>55</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>900</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E18" s="21" t="n">
         <v>140</v>
@@ -2892,13 +2900,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E19" s="21" t="n">
         <v>320</v>
@@ -2907,13 +2915,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>90</v>
@@ -2922,13 +2930,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" s="21" t="n">
         <v>80</v>
@@ -2937,13 +2945,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E22" s="21" t="n">
         <v>150</v>
@@ -2952,13 +2960,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>60</v>
@@ -2967,13 +2975,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E24" s="21" t="n">
         <v>45</v>
@@ -2982,13 +2990,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>83</v>
       </c>
       <c r="E25" s="21" t="n">
         <v>120</v>
@@ -2997,13 +3005,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>100</v>
@@ -3222,7 +3230,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E58" s="23" t="n">
         <f aca="false">SUMIF(D17:D56,"Need",E17:E56)</f>
@@ -3231,7 +3239,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E59" s="23" t="n">
         <f aca="false">SUMIF(D17:D56,"Want",E17:E56)</f>
@@ -3240,7 +3248,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E60" s="25" t="n">
         <f aca="false">SUMIF(C17:C56,"Caregiving",E17:E56)</f>
@@ -3249,7 +3257,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E61" s="27" t="n">
         <f aca="false">SUM(E17:E56)-E58-E59</f>
@@ -3258,7 +3266,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E62" s="29" t="n">
         <f aca="false">E13-E58-E59</f>
@@ -3267,7 +3275,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E63" s="30" t="n">
         <f aca="false">IF(E13&gt;0,E62/E13,0)</f>
@@ -3319,7 +3327,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -3329,7 +3337,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -3339,33 +3347,33 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="21" t="n">
         <v>13</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>0</v>
@@ -3375,18 +3383,18 @@
         <v>13</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="21" t="n">
         <v>35</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>15</v>
@@ -3396,18 +3404,18 @@
         <v>20</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="21" t="n">
         <v>40</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>25</v>
@@ -3417,18 +3425,18 @@
         <v>15</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>3</v>
@@ -3672,7 +3680,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F32" s="29" t="n">
         <f aca="false">SUM(F6:F30)</f>
@@ -3681,7 +3689,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F33" s="29" t="n">
         <f aca="false">F32*12</f>
@@ -3690,7 +3698,7 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
@@ -3742,7 +3750,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -3754,7 +3762,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -3766,33 +3774,33 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C6" s="21" t="n">
         <v>1500</v>
@@ -3821,7 +3829,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C7" s="21" t="n">
         <v>0</v>
@@ -4002,14 +4010,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="37" t="n">
         <f aca="false">SUM(C6:C15)</f>
         <v>1500</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
@@ -4019,7 +4027,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" s="38" t="n">
         <f aca="false">SUM(G6:G15)</f>
@@ -4034,7 +4042,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" s="37" t="n">
         <f aca="false">C18*12</f>
@@ -4049,27 +4057,27 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C24" s="39" t="n">
         <f aca="false">'T · Track'!E7</f>
         <v>2500</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -4079,7 +4087,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C25" s="40" t="n">
         <v>39</v>
@@ -4093,7 +4101,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C26" s="40" t="n">
         <v>4</v>
@@ -4107,7 +4115,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C27" s="40" t="n">
         <v>5</v>
@@ -4121,7 +4129,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C28" s="42" t="n">
         <f aca="false">(N(C25)+N(C26)+N(C27))*52/12</f>
@@ -4136,14 +4144,14 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C29" s="43" t="n">
         <f aca="false">IF(C28&gt;0,C24/C28,0)</f>
         <v>12.0192307692308</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E29" s="32"/>
       <c r="F29" s="32"/>
@@ -4153,7 +4161,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C30" s="44" t="n">
         <v>21</v>
@@ -4167,7 +4175,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C31" s="29" t="n">
         <f aca="false">C29*N(C30)</f>
@@ -4218,7 +4226,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -4228,7 +4236,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -4238,27 +4246,27 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C7" s="39" t="n">
         <f aca="false">'T · Track'!E58</f>
         <v>1740</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E7" s="32"/>
       <c r="F7" s="32"/>
@@ -4266,7 +4274,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C8" s="44" t="n">
         <v>3</v>
@@ -4278,7 +4286,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C9" s="45" t="n">
         <f aca="false">C7</f>
@@ -4291,7 +4299,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="41" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C10" s="23" t="n">
         <f aca="false">C7*N(C8)</f>
@@ -4304,7 +4312,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" s="21" t="n">
         <v>1200</v>
@@ -4312,7 +4320,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="30" t="n">
         <f aca="false">IF(C10&gt;0,MIN(1,N(C11)/C10),0)</f>
@@ -4321,7 +4329,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="21" t="n">
         <v>250</v>
@@ -4329,7 +4337,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" s="35" t="n">
         <f aca="false">IF(N(C11)&gt;=C10,"Done ✓",IF(N(C13)&gt;0,ROUNDUP((C10-N(C11))/C13,0),"Add a transfer"))</f>
@@ -4338,32 +4346,32 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="21" t="n">
         <v>1500</v>
@@ -4385,7 +4393,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C20" s="21" t="n">
         <v>600</v>
@@ -4407,7 +4415,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C21" s="21" t="n">
         <v>1800</v>
@@ -4527,7 +4535,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="41" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E30" s="23" t="n">
         <f aca="false">SUM(E19:E28)</f>
@@ -4536,7 +4544,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E31" s="29" t="n">
         <f aca="false">N(C13)+E30</f>
@@ -4545,7 +4553,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E32" s="23" t="n">
         <f aca="false">'T · Track'!E62-E31</f>
@@ -4554,7 +4562,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="32" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
@@ -4596,7 +4604,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -4604,7 +4612,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -4612,21 +4620,21 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C6" s="40" t="n">
         <v>49</v>
@@ -4635,12 +4643,12 @@
         <v>52</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C7" s="40" t="n">
         <v>43</v>
@@ -4649,12 +4657,12 @@
         <v>40</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C8" s="40" t="n">
         <v>5</v>
@@ -4666,7 +4674,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" s="40" t="n">
         <v>10</v>
@@ -4675,12 +4683,12 @@
         <v>10</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C10" s="40" t="n">
         <v>10</v>
@@ -4689,12 +4697,12 @@
         <v>8</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C11" s="40" t="n">
         <v>12</v>
@@ -4703,12 +4711,12 @@
         <v>16</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C12" s="40" t="n">
         <v>3</v>
@@ -4717,12 +4725,12 @@
         <v>4</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C13" s="40" t="n">
         <v>3</v>
@@ -4731,12 +4739,12 @@
         <v>4</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C14" s="40" t="n">
         <v>10</v>
@@ -4766,7 +4774,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="41" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C19" s="47" t="n">
         <f aca="false">SUM(C6:C17)</f>
@@ -4779,7 +4787,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C20" s="48" t="n">
         <f aca="false">168-C19</f>
@@ -4792,7 +4800,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C22" s="49" t="n">
         <f aca="false">SUMIF(B6:B17,"Family*",D6:D17)-SUMIF(B6:B17,"Family*",C6:C17)</f>
@@ -4801,7 +4809,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C23" s="50" t="n">
         <f aca="false">C22*52</f>
@@ -4810,7 +4818,7 @@
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="32" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
@@ -4824,20 +4832,20 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="41" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C28" s="51" t="n">
         <f aca="false">'U · Understand'!C29</f>
         <v>12.0192307692308</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E28" s="32"/>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="41" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C29" s="23" t="n">
         <f aca="false">MAX(0,SUMIF(B6:B17,"Paid work*",C6:C17)-SUMIF(B6:B17,"Paid work*",D6:D17))*52*C28</f>
@@ -4888,7 +4896,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -4900,7 +4908,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -4912,45 +4920,45 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E6" s="40" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G6" s="21" t="n">
         <v>150</v>
@@ -4960,24 +4968,24 @@
         <v>no time logged</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E7" s="40" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G7" s="21" t="n">
         <v>60</v>
@@ -4987,18 +4995,18 @@
         <v>4.61538461538462</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="20" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E8" s="40" t="n">
         <v>0</v>
@@ -5012,7 +5020,7 @@
         <v/>
       </c>
       <c r="I8" s="20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5186,7 +5194,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G23" s="29" t="n">
         <f aca="false">SUMIF(C6:C21,"&lt;&gt;Career (raise/promotion)",G6:G21)</f>
@@ -5195,7 +5203,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G24" s="23" t="n">
         <f aca="false">SUMIF(C6:C21,"Career (raise/promotion)",G6:G21)</f>
@@ -5204,7 +5212,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E25" s="53" t="n">
         <f aca="false">SUM(E6:E21)</f>
@@ -5213,7 +5221,7 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G26" s="54" t="n">
         <f aca="false">IF('T · Track'!E58&gt;0,G23/'T · Track'!E58,0)</f>
@@ -5222,7 +5230,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="32" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C28" s="32"/>
       <c r="D28" s="32"/>
@@ -5277,7 +5285,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -5286,7 +5294,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -5295,7 +5303,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5318,7 +5326,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C9" s="57" t="n">
         <f aca="false">IF(C14&lt;0,0,IF(C22&lt;C13,1,IF(C20&gt;0,2,IF(C22&lt;C23,3,IF(C25&lt;0.25*C13,4,IF(C25&lt;C13,5,6))))))</f>
@@ -5327,22 +5335,22 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C12" s="58" t="n">
         <f aca="false">'T · Track'!E13</f>
         <v>2560</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F12" s="59" t="n">
         <f aca="false">'U · Understand'!C29</f>
@@ -5351,14 +5359,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C13" s="60" t="n">
         <f aca="false">'T · Track'!E58</f>
         <v>1740</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F13" s="61" t="n">
         <f aca="false">'U · Understand'!C31</f>
@@ -5367,14 +5375,14 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C14" s="61" t="n">
         <f aca="false">'T · Track'!E62</f>
         <v>555</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F14" s="62" t="n">
         <f aca="false">'Income Streams'!E25</f>
@@ -5383,14 +5391,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" s="63" t="n">
         <f aca="false">'T · Track'!E63</f>
         <v>0.216796875</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F15" s="64" t="n">
         <f aca="false">'Income Streams'!G26</f>
@@ -5399,14 +5407,14 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C16" s="65" t="n">
         <f aca="false">'T · Track'!E59</f>
         <v>265</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F16" s="66" t="n">
         <f aca="false">'T · Time'!C22</f>
@@ -5415,14 +5423,14 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C17" s="61" t="n">
         <f aca="false">'R · Reclaim'!F32</f>
         <v>48</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F17" s="58" t="n">
         <f aca="false">'S · Save'!E32</f>
@@ -5431,14 +5439,14 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C18" s="61" t="n">
         <f aca="false">'R · Reclaim'!F33</f>
         <v>576</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F18" s="61" t="n">
         <f aca="false">'Income Streams'!G24</f>
@@ -5447,106 +5455,106 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C20" s="65" t="n">
         <f aca="false">'U · Understand'!C17</f>
         <v>1500</v>
       </c>
       <c r="E20" s="67" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C21" s="65" t="n">
         <f aca="false">'U · Understand'!C19</f>
         <v>298.5</v>
       </c>
       <c r="E21" s="68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F21" s="68"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C22" s="61" t="n">
         <f aca="false">'S · Save'!C11</f>
         <v>1200</v>
       </c>
       <c r="E22" s="68" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F22" s="68"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C23" s="60" t="n">
         <f aca="false">'S · Save'!C10</f>
         <v>5220</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F23" s="68"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C24" s="63" t="n">
         <f aca="false">'S · Save'!C12</f>
         <v>0.229885057471264</v>
       </c>
       <c r="E24" s="68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F24" s="68"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">'Income Streams'!G23</f>
         <v>60</v>
       </c>
       <c r="E25" s="68" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F25" s="68"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E26" s="68" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F26" s="68"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E27" s="68" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F27" s="68"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="69" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="70" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -82,7 +82,7 @@
     <t xml:space="preserve">You work hard for your money. But is it creating the life you're working so hard for?</t>
   </si>
   <si>
-    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and I'm also caring for my mum after her cerebral haemorrhage. I paid off €20,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I live it every week.</t>
+    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and I'm supporting my mum after her cerebral haemorrhage. I paid off €20,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I live it every week.</t>
   </si>
   <si>
     <t xml:space="preserve">You have a demanding career, bills to pay and people who depend on you. You earn a respectable income. Yet despite everything you do, you don't always feel as financially secure or independent as you thought you would.</t>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -82,7 +82,7 @@
     <t xml:space="preserve">You work hard for your money. But is it creating the life you're working so hard for?</t>
   </si>
   <si>
-    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and I'm supporting my mum after her cerebral haemorrhage. I paid off €20,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I live it every week.</t>
+    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and I'm supporting my mum after her cerebral haemorrhage. Everything here comes from my own experience: I paid off €20,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I live it every week.</t>
   </si>
   <si>
     <t xml:space="preserve">You have a demanding career, bills to pay and people who depend on you. You earn a respectable income. Yet despite everything you do, you don't always feel as financially secure or independent as you thought you would.</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">Money going out or still owed (debt)</t>
   </si>
   <si>
-    <t xml:space="preserve">© cybercnslt.com · Liliane Jörger · @cyber_cnslt · For personal use by the purchaser only, please don't resell or share.</t>
+    <t xml:space="preserve">© cybercnslt.com · Liliane · @cyber_cnslt · For personal use by the purchaser only, please don't resell or share.</t>
   </si>
   <si>
     <t xml:space="preserve">T · Track</t>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -82,7 +82,7 @@
     <t xml:space="preserve">You work hard for your money. But is it creating the life you're working so hard for?</t>
   </si>
   <si>
-    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and I'm supporting my mum after her cerebral haemorrhage. Everything here comes from my own experience: I paid off €20,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I live it every week.</t>
+    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and alongside my 9–5 I support my mum, who receives care at home after her cerebral haemorrhage. Balancing both is demanding, so I know how little time is left at the end of the day. Everything here comes from my own experience: I paid off €20,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I live it every week.</t>
   </si>
   <si>
     <t xml:space="preserve">You have a demanding career, bills to pay and people who depend on you. You earn a respectable income. Yet despite everything you do, you don't always feel as financially secure or independent as you thought you would.</t>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="297">
   <si>
     <t xml:space="preserve">Hey, I'm Liliane.</t>
   </si>
@@ -92,6 +92,15 @@
   </si>
   <si>
     <t xml:space="preserve">I know that feeling. I started as a flight attendant working toward becoming a pilot, until COVID changed those plans. I rebuilt my path in cybersecurity consulting. My income grew, but financial security didn't automatically follow. I paid off €20,000 of debt not by first earning more, but by understanding my finances and making deliberate changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHY I REALLY BUILT THIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My mum is 83. When she had her cerebral haemorrhage, I realised how valuable time really is, and how little of it I had left after work. I want to spend as much time with her as I possibly can. Not someday, but now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every plan I found told me to quit my job or hustle harder. None were made for someone with a demanding career and a parent who needs them. I wished I'd had a clear, honest plan for the few hours I actually had. So I built it for myself. You shouldn't need a wake-up call to start.</t>
   </si>
   <si>
     <t xml:space="preserve">That's why I created the TRUST Sheet. No judgment. No unrealistic promises. No complicated jargon. Just a practical starting point for making your money work toward the life you actually want.</t>
@@ -972,7 +981,7 @@
     <numFmt numFmtId="169" formatCode="0"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1037,6 +1046,14 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF9E1B5E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
       <color rgb="FF9E1B5E"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -1208,7 +1225,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1231,6 +1248,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F4F2"/>
         <bgColor rgb="FFF2F8F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7E7EF"/>
+        <bgColor rgb="FFE8F4F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1295,7 +1318,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1324,15 +1347,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1340,27 +1363,31 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1368,27 +1395,95 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1396,99 +1491,31 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1500,15 +1527,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1516,39 +1543,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1568,11 +1595,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1580,7 +1603,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1643,7 +1670,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFF7E7EF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1862,7 +1889,7 @@
     <tabColor rgb="FF9E1B5E"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B34"/>
+  <dimension ref="B2:B38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1900,109 +1927,124 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="s">
+    <row r="11" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
+    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="6" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
+    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
+    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="3" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="7" t="s">
+    <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8" t="s">
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="9" t="s">
+    <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="10" t="s">
+    <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2036,365 +2078,365 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
+      <c r="B2" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
+      <c r="B3" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="G5" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="H5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="I5" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="J5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="E5" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="G5" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="20" t="s">
         <v>270</v>
       </c>
+      <c r="I5" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="C6" s="21" t="n">
+      <c r="B6" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="C6" s="22" t="n">
         <v>2500</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="22" t="n">
         <v>1650</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="22" t="n">
         <v>330</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="32" t="n">
         <f aca="false">IF(C6="","",C6-N(D6)-N(E6))</f>
         <v>520</v>
       </c>
-      <c r="G6" s="46" t="n">
+      <c r="G6" s="47" t="n">
         <f aca="false">IF(N(C6)&gt;0,F6/C6,"")</f>
         <v>0.208</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="22" t="n">
         <v>1000</v>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="22" t="n">
         <v>1500</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="71" t="str">
+      <c r="K6" s="72" t="str">
         <f aca="false">IF(C6="","",INDEX(Lists!$F$1:$F$7,1+IF(F6&lt;0,0,IF(N(H6)&lt;N(D6),1,IF(N(I6)&gt;0,2,IF(N(H6)&lt;N(D6)*'S · Save'!$C$8,3,IF(N(J6)&lt;0.25*N(D6),4,IF(N(J6)&lt;N(D6),5,6))))))))</f>
         <v>Level 1 · Stable</v>
       </c>
-      <c r="L6" s="20" t="s">
-        <v>272</v>
+      <c r="L6" s="21" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="C7" s="21" t="n">
+      <c r="B7" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" s="22" t="n">
         <v>2560</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="22" t="n">
         <v>1640</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="22" t="n">
         <v>265</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="32" t="n">
         <f aca="false">IF(C7="","",C7-N(D7)-N(E7))</f>
         <v>655</v>
       </c>
-      <c r="G7" s="46" t="n">
+      <c r="G7" s="47" t="n">
         <f aca="false">IF(N(C7)&gt;0,F7/C7,"")</f>
         <v>0.255859375</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="22" t="n">
         <v>1200</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="22" t="n">
         <v>1400</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="K7" s="71" t="str">
+      <c r="K7" s="72" t="str">
         <f aca="false">IF(C7="","",INDEX(Lists!$F$1:$F$7,1+IF(F7&lt;0,0,IF(N(H7)&lt;N(D7),1,IF(N(I7)&gt;0,2,IF(N(H7)&lt;N(D7)*'S · Save'!$C$8,3,IF(N(J7)&lt;0.25*N(D7),4,IF(N(J7)&lt;N(D7),5,6))))))))</f>
         <v>Level 1 · Stable</v>
       </c>
-      <c r="L7" s="20" t="s">
-        <v>274</v>
+      <c r="L7" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="20"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="31" t="str">
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="32" t="str">
         <f aca="false">IF(C8="","",C8-N(D8)-N(E8))</f>
         <v/>
       </c>
-      <c r="G8" s="46" t="str">
+      <c r="G8" s="47" t="str">
         <f aca="false">IF(N(C8)&gt;0,F8/C8,"")</f>
         <v/>
       </c>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="71" t="str">
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="72" t="str">
         <f aca="false">IF(C8="","",INDEX(Lists!$F$1:$F$7,1+IF(F8&lt;0,0,IF(N(H8)&lt;N(D8),1,IF(N(I8)&gt;0,2,IF(N(H8)&lt;N(D8)*'S · Save'!$C$8,3,IF(N(J8)&lt;0.25*N(D8),4,IF(N(J8)&lt;N(D8),5,6))))))))</f>
         <v/>
       </c>
-      <c r="L8" s="20"/>
+      <c r="L8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="31" t="str">
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="32" t="str">
         <f aca="false">IF(C9="","",C9-N(D9)-N(E9))</f>
         <v/>
       </c>
-      <c r="G9" s="46" t="str">
+      <c r="G9" s="47" t="str">
         <f aca="false">IF(N(C9)&gt;0,F9/C9,"")</f>
         <v/>
       </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="71" t="str">
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="72" t="str">
         <f aca="false">IF(C9="","",INDEX(Lists!$F$1:$F$7,1+IF(F9&lt;0,0,IF(N(H9)&lt;N(D9),1,IF(N(I9)&gt;0,2,IF(N(H9)&lt;N(D9)*'S · Save'!$C$8,3,IF(N(J9)&lt;0.25*N(D9),4,IF(N(J9)&lt;N(D9),5,6))))))))</f>
         <v/>
       </c>
-      <c r="L9" s="20"/>
+      <c r="L9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="31" t="str">
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="32" t="str">
         <f aca="false">IF(C10="","",C10-N(D10)-N(E10))</f>
         <v/>
       </c>
-      <c r="G10" s="46" t="str">
+      <c r="G10" s="47" t="str">
         <f aca="false">IF(N(C10)&gt;0,F10/C10,"")</f>
         <v/>
       </c>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="71" t="str">
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="72" t="str">
         <f aca="false">IF(C10="","",INDEX(Lists!$F$1:$F$7,1+IF(F10&lt;0,0,IF(N(H10)&lt;N(D10),1,IF(N(I10)&gt;0,2,IF(N(H10)&lt;N(D10)*'S · Save'!$C$8,3,IF(N(J10)&lt;0.25*N(D10),4,IF(N(J10)&lt;N(D10),5,6))))))))</f>
         <v/>
       </c>
-      <c r="L10" s="20"/>
+      <c r="L10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="31" t="str">
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="32" t="str">
         <f aca="false">IF(C11="","",C11-N(D11)-N(E11))</f>
         <v/>
       </c>
-      <c r="G11" s="46" t="str">
+      <c r="G11" s="47" t="str">
         <f aca="false">IF(N(C11)&gt;0,F11/C11,"")</f>
         <v/>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="71" t="str">
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="72" t="str">
         <f aca="false">IF(C11="","",INDEX(Lists!$F$1:$F$7,1+IF(F11&lt;0,0,IF(N(H11)&lt;N(D11),1,IF(N(I11)&gt;0,2,IF(N(H11)&lt;N(D11)*'S · Save'!$C$8,3,IF(N(J11)&lt;0.25*N(D11),4,IF(N(J11)&lt;N(D11),5,6))))))))</f>
         <v/>
       </c>
-      <c r="L11" s="20"/>
+      <c r="L11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="31" t="str">
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="32" t="str">
         <f aca="false">IF(C12="","",C12-N(D12)-N(E12))</f>
         <v/>
       </c>
-      <c r="G12" s="46" t="str">
+      <c r="G12" s="47" t="str">
         <f aca="false">IF(N(C12)&gt;0,F12/C12,"")</f>
         <v/>
       </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="71" t="str">
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="72" t="str">
         <f aca="false">IF(C12="","",INDEX(Lists!$F$1:$F$7,1+IF(F12&lt;0,0,IF(N(H12)&lt;N(D12),1,IF(N(I12)&gt;0,2,IF(N(H12)&lt;N(D12)*'S · Save'!$C$8,3,IF(N(J12)&lt;0.25*N(D12),4,IF(N(J12)&lt;N(D12),5,6))))))))</f>
         <v/>
       </c>
-      <c r="L12" s="20"/>
+      <c r="L12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="31" t="str">
+      <c r="B13" s="21"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="32" t="str">
         <f aca="false">IF(C13="","",C13-N(D13)-N(E13))</f>
         <v/>
       </c>
-      <c r="G13" s="46" t="str">
+      <c r="G13" s="47" t="str">
         <f aca="false">IF(N(C13)&gt;0,F13/C13,"")</f>
         <v/>
       </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="71" t="str">
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="72" t="str">
         <f aca="false">IF(C13="","",INDEX(Lists!$F$1:$F$7,1+IF(F13&lt;0,0,IF(N(H13)&lt;N(D13),1,IF(N(I13)&gt;0,2,IF(N(H13)&lt;N(D13)*'S · Save'!$C$8,3,IF(N(J13)&lt;0.25*N(D13),4,IF(N(J13)&lt;N(D13),5,6))))))))</f>
         <v/>
       </c>
-      <c r="L13" s="20"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="31" t="str">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="32" t="str">
         <f aca="false">IF(C14="","",C14-N(D14)-N(E14))</f>
         <v/>
       </c>
-      <c r="G14" s="46" t="str">
+      <c r="G14" s="47" t="str">
         <f aca="false">IF(N(C14)&gt;0,F14/C14,"")</f>
         <v/>
       </c>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="71" t="str">
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="72" t="str">
         <f aca="false">IF(C14="","",INDEX(Lists!$F$1:$F$7,1+IF(F14&lt;0,0,IF(N(H14)&lt;N(D14),1,IF(N(I14)&gt;0,2,IF(N(H14)&lt;N(D14)*'S · Save'!$C$8,3,IF(N(J14)&lt;0.25*N(D14),4,IF(N(J14)&lt;N(D14),5,6))))))))</f>
         <v/>
       </c>
-      <c r="L14" s="20"/>
+      <c r="L14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="31" t="str">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="32" t="str">
         <f aca="false">IF(C15="","",C15-N(D15)-N(E15))</f>
         <v/>
       </c>
-      <c r="G15" s="46" t="str">
+      <c r="G15" s="47" t="str">
         <f aca="false">IF(N(C15)&gt;0,F15/C15,"")</f>
         <v/>
       </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="71" t="str">
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="72" t="str">
         <f aca="false">IF(C15="","",INDEX(Lists!$F$1:$F$7,1+IF(F15&lt;0,0,IF(N(H15)&lt;N(D15),1,IF(N(I15)&gt;0,2,IF(N(H15)&lt;N(D15)*'S · Save'!$C$8,3,IF(N(J15)&lt;0.25*N(D15),4,IF(N(J15)&lt;N(D15),5,6))))))))</f>
         <v/>
       </c>
-      <c r="L15" s="20"/>
+      <c r="L15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="31" t="str">
+      <c r="B16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="32" t="str">
         <f aca="false">IF(C16="","",C16-N(D16)-N(E16))</f>
         <v/>
       </c>
-      <c r="G16" s="46" t="str">
+      <c r="G16" s="47" t="str">
         <f aca="false">IF(N(C16)&gt;0,F16/C16,"")</f>
         <v/>
       </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="71" t="str">
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="72" t="str">
         <f aca="false">IF(C16="","",INDEX(Lists!$F$1:$F$7,1+IF(F16&lt;0,0,IF(N(H16)&lt;N(D16),1,IF(N(I16)&gt;0,2,IF(N(H16)&lt;N(D16)*'S · Save'!$C$8,3,IF(N(J16)&lt;0.25*N(D16),4,IF(N(J16)&lt;N(D16),5,6))))))))</f>
         <v/>
       </c>
-      <c r="L16" s="20"/>
+      <c r="L16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="31" t="str">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="32" t="str">
         <f aca="false">IF(C17="","",C17-N(D17)-N(E17))</f>
         <v/>
       </c>
-      <c r="G17" s="46" t="str">
+      <c r="G17" s="47" t="str">
         <f aca="false">IF(N(C17)&gt;0,F17/C17,"")</f>
         <v/>
       </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="71" t="str">
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="72" t="str">
         <f aca="false">IF(C17="","",INDEX(Lists!$F$1:$F$7,1+IF(F17&lt;0,0,IF(N(H17)&lt;N(D17),1,IF(N(I17)&gt;0,2,IF(N(H17)&lt;N(D17)*'S · Save'!$C$8,3,IF(N(J17)&lt;0.25*N(D17),4,IF(N(J17)&lt;N(D17),5,6))))))))</f>
         <v/>
       </c>
-      <c r="L17" s="20"/>
+      <c r="L17" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2421,160 +2463,160 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -2604,120 +2646,120 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="11"/>
+      <c r="B2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="12"/>
+      <c r="B3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="s">
-        <v>29</v>
+      <c r="B5" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>31</v>
+      <c r="B6" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>33</v>
+      <c r="B7" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>35</v>
+      <c r="B8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>37</v>
+      <c r="B9" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="14"/>
-      <c r="C10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13" t="s">
-        <v>38</v>
+      <c r="B11" s="14" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>40</v>
+      <c r="B12" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>42</v>
+      <c r="B13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="14"/>
-      <c r="C14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="16"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="13" t="s">
-        <v>43</v>
+      <c r="B15" s="14" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>45</v>
+      <c r="B16" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>47</v>
+      <c r="B17" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>49</v>
+      <c r="B18" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="14"/>
-      <c r="C20" s="15" t="s">
-        <v>50</v>
+      <c r="B20" s="15"/>
+      <c r="C20" s="16" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2753,531 +2795,531 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+      <c r="B2" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="B3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="18" t="s">
-        <v>53</v>
+      <c r="B5" s="19" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>56</v>
+      <c r="B6" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="21" t="n">
+      <c r="B7" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="22" t="n">
         <v>2500</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="22" t="n">
+      <c r="B8" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="23" t="n">
         <f aca="false">'Income Streams'!G23</f>
         <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" s="21" t="n">
+      <c r="B9" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="E10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="E10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="E11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="E11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="E12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="E12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="23" t="n">
+      <c r="B13" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="24" t="n">
         <f aca="false">SUM(E7:E12)</f>
         <v>2560</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="18" t="s">
-        <v>64</v>
+      <c r="B15" s="19" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>55</v>
+      <c r="B16" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="21" t="n">
+      <c r="B17" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="22" t="n">
         <v>900</v>
       </c>
-      <c r="F17" s="20" t="s">
-        <v>71</v>
+      <c r="F17" s="21" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="20" t="s">
+      <c r="B18" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" s="21" t="n">
+      <c r="E18" s="22" t="n">
         <v>140</v>
       </c>
-      <c r="F18" s="20"/>
+      <c r="F18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="21" t="n">
+      <c r="B19" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="22" t="n">
         <v>320</v>
       </c>
-      <c r="F19" s="20"/>
+      <c r="F19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="21" t="n">
+      <c r="B20" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="22" t="n">
         <v>90</v>
       </c>
-      <c r="F20" s="20"/>
+      <c r="F20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="21" t="n">
+      <c r="B21" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="20"/>
+      <c r="C21" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="21" t="n">
+      <c r="B22" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="22" t="n">
         <v>150</v>
       </c>
-      <c r="F22" s="20"/>
+      <c r="F22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" s="21" t="n">
+      <c r="B23" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="F23" s="20"/>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="21" t="n">
+      <c r="B24" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="22" t="n">
         <v>45</v>
       </c>
-      <c r="F24" s="20"/>
+      <c r="F24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="21" t="n">
+      <c r="B25" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="22" t="n">
         <v>120</v>
       </c>
-      <c r="F25" s="20"/>
+      <c r="F25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="21" t="n">
+      <c r="E26" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="F26" s="20"/>
+      <c r="F26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="20"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="20"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="20"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="20"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="20"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="20"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="21"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="20"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="21"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="20"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="20"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="20"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="20"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="20"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="20"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="20"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="21"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="20"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="20"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="20"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="21"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="20"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="21"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="20"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="21"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="20"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="20"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="21"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="20"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="20"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="21"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="20"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="20"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="21"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="20"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="21"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="20"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="20"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="21"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="20"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="20"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="21"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="20"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="20"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="21"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="20"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="20"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="21"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="20"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="21"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="20"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="20"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="21"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="20"/>
-      <c r="C56" s="20"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="20"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="21"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E58" s="23" t="n">
+      <c r="B58" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="E58" s="24" t="n">
         <f aca="false">SUMIF(D17:D56,"Need",E17:E56)</f>
         <v>1740</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E59" s="23" t="n">
+      <c r="B59" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E59" s="24" t="n">
         <f aca="false">SUMIF(D17:D56,"Want",E17:E56)</f>
         <v>265</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E60" s="25" t="n">
+      <c r="B60" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E60" s="26" t="n">
         <f aca="false">SUMIF(C17:C56,"Caregiving",E17:E56)</f>
         <v>150</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="E61" s="27" t="n">
+      <c r="B61" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="E61" s="28" t="n">
         <f aca="false">SUM(E17:E56)-E58-E59</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E62" s="29" t="n">
+      <c r="B62" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E62" s="30" t="n">
         <f aca="false">E13-E58-E59</f>
         <v>555</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="E63" s="30" t="n">
+      <c r="B63" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E63" s="31" t="n">
         <f aca="false">IF(E13&gt;0,E62/E13,0)</f>
         <v>0.216796875</v>
       </c>
@@ -3326,385 +3368,385 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
+      <c r="B2" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="B3" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>102</v>
       </c>
+      <c r="E5" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="21" t="n">
+      <c r="B6" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="21" t="n">
+      <c r="D6" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="32" t="n">
         <f aca="false">IF(OR(C6="",D6="",D6="Keep"),0,MAX(0,C6-N(E6)))</f>
         <v>13</v>
       </c>
-      <c r="G6" s="20" t="s">
-        <v>105</v>
+      <c r="G6" s="21" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="21" t="n">
+      <c r="B7" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="22" t="n">
         <v>35</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="21" t="n">
+      <c r="D7" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="32" t="n">
         <f aca="false">IF(OR(C7="",D7="",D7="Keep"),0,MAX(0,C7-N(E7)))</f>
         <v>20</v>
       </c>
-      <c r="G7" s="20" t="s">
-        <v>108</v>
+      <c r="G7" s="21" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="21" t="n">
+      <c r="B8" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" s="21" t="n">
+      <c r="D8" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="32" t="n">
         <f aca="false">IF(OR(C8="",D8="",D8="Keep"),0,MAX(0,C8-N(E8)))</f>
         <v>15</v>
       </c>
-      <c r="G8" s="20" t="s">
-        <v>111</v>
+      <c r="G8" s="21" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="21" t="n">
+      <c r="B9" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="21" t="n">
+      <c r="D9" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="31" t="n">
+      <c r="F9" s="32" t="n">
         <f aca="false">IF(OR(C9="",D9="",D9="Keep"),0,MAX(0,C9-N(E9)))</f>
         <v>0</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="31" t="n">
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="32" t="n">
         <f aca="false">IF(OR(C10="",D10="",D10="Keep"),0,MAX(0,C10-N(E10)))</f>
         <v>0</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="31" t="n">
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="32" t="n">
         <f aca="false">IF(OR(C11="",D11="",D11="Keep"),0,MAX(0,C11-N(E11)))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="20"/>
+      <c r="G11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="31" t="n">
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="32" t="n">
         <f aca="false">IF(OR(C12="",D12="",D12="Keep"),0,MAX(0,C12-N(E12)))</f>
         <v>0</v>
       </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="31" t="n">
+      <c r="B13" s="21"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="32" t="n">
         <f aca="false">IF(OR(C13="",D13="",D13="Keep"),0,MAX(0,C13-N(E13)))</f>
         <v>0</v>
       </c>
-      <c r="G13" s="20"/>
+      <c r="G13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="31" t="n">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="32" t="n">
         <f aca="false">IF(OR(C14="",D14="",D14="Keep"),0,MAX(0,C14-N(E14)))</f>
         <v>0</v>
       </c>
-      <c r="G14" s="20"/>
+      <c r="G14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="31" t="n">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="32" t="n">
         <f aca="false">IF(OR(C15="",D15="",D15="Keep"),0,MAX(0,C15-N(E15)))</f>
         <v>0</v>
       </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="31" t="n">
+      <c r="B16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="32" t="n">
         <f aca="false">IF(OR(C16="",D16="",D16="Keep"),0,MAX(0,C16-N(E16)))</f>
         <v>0</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="31" t="n">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="32" t="n">
         <f aca="false">IF(OR(C17="",D17="",D17="Keep"),0,MAX(0,C17-N(E17)))</f>
         <v>0</v>
       </c>
-      <c r="G17" s="20"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="20"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="31" t="n">
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="32" t="n">
         <f aca="false">IF(OR(C18="",D18="",D18="Keep"),0,MAX(0,C18-N(E18)))</f>
         <v>0</v>
       </c>
-      <c r="G18" s="20"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="31" t="n">
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="32" t="n">
         <f aca="false">IF(OR(C19="",D19="",D19="Keep"),0,MAX(0,C19-N(E19)))</f>
         <v>0</v>
       </c>
-      <c r="G19" s="20"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="20"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="31" t="n">
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="32" t="n">
         <f aca="false">IF(OR(C20="",D20="",D20="Keep"),0,MAX(0,C20-N(E20)))</f>
         <v>0</v>
       </c>
-      <c r="G20" s="20"/>
+      <c r="G20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="20"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="31" t="n">
+      <c r="B21" s="21"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="32" t="n">
         <f aca="false">IF(OR(C21="",D21="",D21="Keep"),0,MAX(0,C21-N(E21)))</f>
         <v>0</v>
       </c>
-      <c r="G21" s="20"/>
+      <c r="G21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="20"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="31" t="n">
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="32" t="n">
         <f aca="false">IF(OR(C22="",D22="",D22="Keep"),0,MAX(0,C22-N(E22)))</f>
         <v>0</v>
       </c>
-      <c r="G22" s="20"/>
+      <c r="G22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="20"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="31" t="n">
+      <c r="B23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="32" t="n">
         <f aca="false">IF(OR(C23="",D23="",D23="Keep"),0,MAX(0,C23-N(E23)))</f>
         <v>0</v>
       </c>
-      <c r="G23" s="20"/>
+      <c r="G23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="20"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="31" t="n">
+      <c r="B24" s="21"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="32" t="n">
         <f aca="false">IF(OR(C24="",D24="",D24="Keep"),0,MAX(0,C24-N(E24)))</f>
         <v>0</v>
       </c>
-      <c r="G24" s="20"/>
+      <c r="G24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="20"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="31" t="n">
+      <c r="B25" s="21"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="32" t="n">
         <f aca="false">IF(OR(C25="",D25="",D25="Keep"),0,MAX(0,C25-N(E25)))</f>
         <v>0</v>
       </c>
-      <c r="G25" s="20"/>
+      <c r="G25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="20"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="31" t="n">
+      <c r="B26" s="21"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="32" t="n">
         <f aca="false">IF(OR(C26="",D26="",D26="Keep"),0,MAX(0,C26-N(E26)))</f>
         <v>0</v>
       </c>
-      <c r="G26" s="20"/>
+      <c r="G26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="20"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="31" t="n">
+      <c r="B27" s="21"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="32" t="n">
         <f aca="false">IF(OR(C27="",D27="",D27="Keep"),0,MAX(0,C27-N(E27)))</f>
         <v>0</v>
       </c>
-      <c r="G27" s="20"/>
+      <c r="G27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="20"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="31" t="n">
+      <c r="B28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="32" t="n">
         <f aca="false">IF(OR(C28="",D28="",D28="Keep"),0,MAX(0,C28-N(E28)))</f>
         <v>0</v>
       </c>
-      <c r="G28" s="20"/>
+      <c r="G28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="20"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="31" t="n">
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="32" t="n">
         <f aca="false">IF(OR(C29="",D29="",D29="Keep"),0,MAX(0,C29-N(E29)))</f>
         <v>0</v>
       </c>
-      <c r="G29" s="20"/>
+      <c r="G29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="20"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="31" t="n">
+      <c r="B30" s="21"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="32" t="n">
         <f aca="false">IF(OR(C30="",D30="",D30="Keep"),0,MAX(0,C30-N(E30)))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="20"/>
+      <c r="G30" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32" s="29" t="n">
+      <c r="B32" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32" s="30" t="n">
         <f aca="false">SUM(F6:F30)</f>
         <v>48</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="F33" s="29" t="n">
+      <c r="B33" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33" s="30" t="n">
         <f aca="false">F32*12</f>
         <v>576</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
+      <c r="B35" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3749,444 +3791,444 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
+      <c r="B2" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
+      <c r="B3" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="E5" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="F5" s="20" t="s">
         <v>126</v>
       </c>
+      <c r="G5" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="21" t="n">
+      <c r="B6" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="22" t="n">
         <v>1500</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="34" t="n">
         <v>0.199</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="G6" s="34" t="n">
+      <c r="G6" s="35" t="n">
         <f aca="false">IF(N(C6)&gt;0,C6*N(D6)/12,0)</f>
         <v>24.875</v>
       </c>
-      <c r="H6" s="35" t="n">
+      <c r="H6" s="36" t="n">
         <f aca="false">IF(N(C6)&lt;=0,"",IF(N(E6)+N(F6)&lt;=G6,"Payment too low",ROUNDUP(IF(N(D6)=0,C6/(N(E6)+N(F6)),NPER(D6/12,-(N(E6)+N(F6)),C6)),0)))</f>
         <v>18</v>
       </c>
-      <c r="I6" s="36" t="n">
+      <c r="I6" s="37" t="n">
         <f aca="false">IF(N(C6)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D6))+1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C7" s="21" t="n">
+      <c r="B7" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="34" t="n">
         <v>0.12</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="34" t="n">
+      <c r="G7" s="35" t="n">
         <f aca="false">IF(N(C7)&gt;0,C7*N(D7)/12,0)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="35" t="str">
+      <c r="H7" s="36" t="str">
         <f aca="false">IF(N(C7)&lt;=0,"",IF(N(E7)+N(F7)&lt;=G7,"Payment too low",ROUNDUP(IF(N(D7)=0,C7/(N(E7)+N(F7)),NPER(D7/12,-(N(E7)+N(F7)),C7)),0)))</f>
         <v/>
       </c>
-      <c r="I7" s="36" t="str">
+      <c r="I7" s="37" t="str">
         <f aca="false">IF(N(C7)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D7))+1)</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="20"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="34" t="n">
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="35" t="n">
         <f aca="false">IF(N(C8)&gt;0,C8*N(D8)/12,0)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="35" t="str">
+      <c r="H8" s="36" t="str">
         <f aca="false">IF(N(C8)&lt;=0,"",IF(N(E8)+N(F8)&lt;=G8,"Payment too low",ROUNDUP(IF(N(D8)=0,C8/(N(E8)+N(F8)),NPER(D8/12,-(N(E8)+N(F8)),C8)),0)))</f>
         <v/>
       </c>
-      <c r="I8" s="36" t="str">
+      <c r="I8" s="37" t="str">
         <f aca="false">IF(N(C8)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D8))+1)</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="34" t="n">
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="35" t="n">
         <f aca="false">IF(N(C9)&gt;0,C9*N(D9)/12,0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="35" t="str">
+      <c r="H9" s="36" t="str">
         <f aca="false">IF(N(C9)&lt;=0,"",IF(N(E9)+N(F9)&lt;=G9,"Payment too low",ROUNDUP(IF(N(D9)=0,C9/(N(E9)+N(F9)),NPER(D9/12,-(N(E9)+N(F9)),C9)),0)))</f>
         <v/>
       </c>
-      <c r="I9" s="36" t="str">
+      <c r="I9" s="37" t="str">
         <f aca="false">IF(N(C9)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D9))+1)</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="34" t="n">
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="35" t="n">
         <f aca="false">IF(N(C10)&gt;0,C10*N(D10)/12,0)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="35" t="str">
+      <c r="H10" s="36" t="str">
         <f aca="false">IF(N(C10)&lt;=0,"",IF(N(E10)+N(F10)&lt;=G10,"Payment too low",ROUNDUP(IF(N(D10)=0,C10/(N(E10)+N(F10)),NPER(D10/12,-(N(E10)+N(F10)),C10)),0)))</f>
         <v/>
       </c>
-      <c r="I10" s="36" t="str">
+      <c r="I10" s="37" t="str">
         <f aca="false">IF(N(C10)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D10))+1)</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="34" t="n">
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="35" t="n">
         <f aca="false">IF(N(C11)&gt;0,C11*N(D11)/12,0)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="35" t="str">
+      <c r="H11" s="36" t="str">
         <f aca="false">IF(N(C11)&lt;=0,"",IF(N(E11)+N(F11)&lt;=G11,"Payment too low",ROUNDUP(IF(N(D11)=0,C11/(N(E11)+N(F11)),NPER(D11/12,-(N(E11)+N(F11)),C11)),0)))</f>
         <v/>
       </c>
-      <c r="I11" s="36" t="str">
+      <c r="I11" s="37" t="str">
         <f aca="false">IF(N(C11)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D11))+1)</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="34" t="n">
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="35" t="n">
         <f aca="false">IF(N(C12)&gt;0,C12*N(D12)/12,0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="35" t="str">
+      <c r="H12" s="36" t="str">
         <f aca="false">IF(N(C12)&lt;=0,"",IF(N(E12)+N(F12)&lt;=G12,"Payment too low",ROUNDUP(IF(N(D12)=0,C12/(N(E12)+N(F12)),NPER(D12/12,-(N(E12)+N(F12)),C12)),0)))</f>
         <v/>
       </c>
-      <c r="I12" s="36" t="str">
+      <c r="I12" s="37" t="str">
         <f aca="false">IF(N(C12)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D12))+1)</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="34" t="n">
+      <c r="B13" s="21"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="35" t="n">
         <f aca="false">IF(N(C13)&gt;0,C13*N(D13)/12,0)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="35" t="str">
+      <c r="H13" s="36" t="str">
         <f aca="false">IF(N(C13)&lt;=0,"",IF(N(E13)+N(F13)&lt;=G13,"Payment too low",ROUNDUP(IF(N(D13)=0,C13/(N(E13)+N(F13)),NPER(D13/12,-(N(E13)+N(F13)),C13)),0)))</f>
         <v/>
       </c>
-      <c r="I13" s="36" t="str">
+      <c r="I13" s="37" t="str">
         <f aca="false">IF(N(C13)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D13))+1)</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="34" t="n">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="35" t="n">
         <f aca="false">IF(N(C14)&gt;0,C14*N(D14)/12,0)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="35" t="str">
+      <c r="H14" s="36" t="str">
         <f aca="false">IF(N(C14)&lt;=0,"",IF(N(E14)+N(F14)&lt;=G14,"Payment too low",ROUNDUP(IF(N(D14)=0,C14/(N(E14)+N(F14)),NPER(D14/12,-(N(E14)+N(F14)),C14)),0)))</f>
         <v/>
       </c>
-      <c r="I14" s="36" t="str">
+      <c r="I14" s="37" t="str">
         <f aca="false">IF(N(C14)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D14))+1)</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="34" t="n">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="35" t="n">
         <f aca="false">IF(N(C15)&gt;0,C15*N(D15)/12,0)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="35" t="str">
+      <c r="H15" s="36" t="str">
         <f aca="false">IF(N(C15)&lt;=0,"",IF(N(E15)+N(F15)&lt;=G15,"Payment too low",ROUNDUP(IF(N(D15)=0,C15/(N(E15)+N(F15)),NPER(D15/12,-(N(E15)+N(F15)),C15)),0)))</f>
         <v/>
       </c>
-      <c r="I15" s="36" t="str">
+      <c r="I15" s="37" t="str">
         <f aca="false">IF(N(C15)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D15))+1)</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" s="37" t="n">
+      <c r="B17" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="38" t="n">
         <f aca="false">SUM(C6:C15)</f>
         <v>1500</v>
       </c>
-      <c r="D17" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
+      <c r="D17" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="38" t="n">
+      <c r="B18" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="39" t="n">
         <f aca="false">SUM(G6:G15)</f>
         <v>24.875</v>
       </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" s="37" t="n">
+      <c r="B19" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="38" t="n">
         <f aca="false">C18*12</f>
         <v>298.5</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="18" t="s">
-        <v>133</v>
+      <c r="B22" s="19" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>135</v>
+      <c r="B23" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="C24" s="39" t="n">
+      <c r="B24" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="40" t="n">
         <f aca="false">'T · Track'!E7</f>
         <v>2500</v>
       </c>
-      <c r="D24" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
+      <c r="D24" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="40" t="n">
+      <c r="B25" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="41" t="n">
         <v>39</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="C26" s="40" t="n">
+      <c r="B26" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C27" s="40" t="n">
+      <c r="B27" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="41" t="s">
-        <v>141</v>
-      </c>
-      <c r="C28" s="42" t="n">
+      <c r="B28" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="43" t="n">
         <f aca="false">(N(C25)+N(C26)+N(C27))*52/12</f>
         <v>208</v>
       </c>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="C29" s="43" t="n">
+      <c r="B29" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" s="44" t="n">
         <f aca="false">IF(C28&gt;0,C24/C28,0)</f>
         <v>12.0192307692308</v>
       </c>
-      <c r="D29" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
+      <c r="D29" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="C30" s="44" t="n">
+      <c r="B30" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C30" s="45" t="n">
         <v>21</v>
       </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="C31" s="29" t="n">
+      <c r="B31" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="C31" s="30" t="n">
         <f aca="false">C29*N(C30)</f>
         <v>252.403846153846</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4225,350 +4267,350 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
+      <c r="B2" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="B3" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="18" t="s">
-        <v>148</v>
+      <c r="B5" s="19" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>135</v>
+      <c r="B6" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="39" t="n">
+      <c r="B7" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="40" t="n">
         <f aca="false">'T · Track'!E58</f>
         <v>1740</v>
       </c>
-      <c r="D7" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
+      <c r="D7" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="44" t="n">
+      <c r="B8" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="41" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" s="45" t="n">
+      <c r="B9" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="46" t="n">
         <f aca="false">C7</f>
         <v>1740</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="41" t="s">
-        <v>153</v>
-      </c>
-      <c r="C10" s="23" t="n">
+      <c r="B10" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="24" t="n">
         <f aca="false">C7*N(C8)</f>
         <v>5220</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="C11" s="21" t="n">
+      <c r="B11" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" s="22" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="C12" s="30" t="n">
+      <c r="B12" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="31" t="n">
         <f aca="false">IF(C10&gt;0,MIN(1,N(C11)/C10),0)</f>
         <v>0.229885057471264</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="21" t="n">
+      <c r="B13" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="22" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="C14" s="35" t="n">
+      <c r="B14" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="36" t="n">
         <f aca="false">IF(N(C11)&gt;=C10,"Done ✓",IF(N(C13)&gt;0,ROUNDUP((C10-N(C11))/C13,0),"Add a transfer"))</f>
         <v>17</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="19" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" s="20" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>155</v>
-      </c>
-    </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="C19" s="21" t="n">
+      <c r="B19" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="C19" s="22" t="n">
         <v>1500</v>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="22" t="n">
         <v>300</v>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="E19" s="22" t="n">
         <v>75</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="36" t="n">
         <f aca="false">IF(N(C19)=0,"",IF(N(D19)&gt;=C19,"Done ✓",IF(N(E19)&gt;0,ROUNDUP((C19-N(D19))/E19,0),"–")))</f>
         <v>16</v>
       </c>
-      <c r="G19" s="46" t="n">
+      <c r="G19" s="47" t="n">
         <f aca="false">IF(N(C19)&gt;0,MIN(1,N(D19)/C19),0)</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="C20" s="21" t="n">
+      <c r="B20" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C20" s="22" t="n">
         <v>600</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="E20" s="21" t="n">
+      <c r="E20" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="35" t="n">
+      <c r="F20" s="36" t="n">
         <f aca="false">IF(N(C20)=0,"",IF(N(D20)&gt;=C20,"Done ✓",IF(N(E20)&gt;0,ROUNDUP((C20-N(D20))/E20,0),"–")))</f>
         <v>10</v>
       </c>
-      <c r="G20" s="46" t="n">
+      <c r="G20" s="47" t="n">
         <f aca="false">IF(N(C20)&gt;0,MIN(1,N(D20)/C20),0)</f>
         <v>0.166666666666667</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="C21" s="21" t="n">
+      <c r="B21" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="22" t="n">
         <v>1800</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="22" t="n">
         <v>250</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="F21" s="35" t="n">
+      <c r="F21" s="36" t="n">
         <f aca="false">IF(N(C21)=0,"",IF(N(D21)&gt;=C21,"Done ✓",IF(N(E21)&gt;0,ROUNDUP((C21-N(D21))/E21,0),"–")))</f>
         <v>16</v>
       </c>
-      <c r="G21" s="46" t="n">
+      <c r="G21" s="47" t="n">
         <f aca="false">IF(N(C21)&gt;0,MIN(1,N(D21)/C21),0)</f>
         <v>0.138888888888889</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="20"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="35" t="str">
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="36" t="str">
         <f aca="false">IF(N(C22)=0,"",IF(N(D22)&gt;=C22,"Done ✓",IF(N(E22)&gt;0,ROUNDUP((C22-N(D22))/E22,0),"–")))</f>
         <v/>
       </c>
-      <c r="G22" s="46" t="n">
+      <c r="G22" s="47" t="n">
         <f aca="false">IF(N(C22)&gt;0,MIN(1,N(D22)/C22),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="20"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="35" t="str">
+      <c r="B23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="36" t="str">
         <f aca="false">IF(N(C23)=0,"",IF(N(D23)&gt;=C23,"Done ✓",IF(N(E23)&gt;0,ROUNDUP((C23-N(D23))/E23,0),"–")))</f>
         <v/>
       </c>
-      <c r="G23" s="46" t="n">
+      <c r="G23" s="47" t="n">
         <f aca="false">IF(N(C23)&gt;0,MIN(1,N(D23)/C23),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="20"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="35" t="str">
+      <c r="B24" s="21"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="36" t="str">
         <f aca="false">IF(N(C24)=0,"",IF(N(D24)&gt;=C24,"Done ✓",IF(N(E24)&gt;0,ROUNDUP((C24-N(D24))/E24,0),"–")))</f>
         <v/>
       </c>
-      <c r="G24" s="46" t="n">
+      <c r="G24" s="47" t="n">
         <f aca="false">IF(N(C24)&gt;0,MIN(1,N(D24)/C24),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="20"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="35" t="str">
+      <c r="B25" s="21"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="36" t="str">
         <f aca="false">IF(N(C25)=0,"",IF(N(D25)&gt;=C25,"Done ✓",IF(N(E25)&gt;0,ROUNDUP((C25-N(D25))/E25,0),"–")))</f>
         <v/>
       </c>
-      <c r="G25" s="46" t="n">
+      <c r="G25" s="47" t="n">
         <f aca="false">IF(N(C25)&gt;0,MIN(1,N(D25)/C25),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="20"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="35" t="str">
+      <c r="B26" s="21"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="36" t="str">
         <f aca="false">IF(N(C26)=0,"",IF(N(D26)&gt;=C26,"Done ✓",IF(N(E26)&gt;0,ROUNDUP((C26-N(D26))/E26,0),"–")))</f>
         <v/>
       </c>
-      <c r="G26" s="46" t="n">
+      <c r="G26" s="47" t="n">
         <f aca="false">IF(N(C26)&gt;0,MIN(1,N(D26)/C26),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="20"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="35" t="str">
+      <c r="B27" s="21"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="36" t="str">
         <f aca="false">IF(N(C27)=0,"",IF(N(D27)&gt;=C27,"Done ✓",IF(N(E27)&gt;0,ROUNDUP((C27-N(D27))/E27,0),"–")))</f>
         <v/>
       </c>
-      <c r="G27" s="46" t="n">
+      <c r="G27" s="47" t="n">
         <f aca="false">IF(N(C27)&gt;0,MIN(1,N(D27)/C27),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="20"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="35" t="str">
+      <c r="B28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="36" t="str">
         <f aca="false">IF(N(C28)=0,"",IF(N(D28)&gt;=C28,"Done ✓",IF(N(E28)&gt;0,ROUNDUP((C28-N(D28))/E28,0),"–")))</f>
         <v/>
       </c>
-      <c r="G28" s="46" t="n">
+      <c r="G28" s="47" t="n">
         <f aca="false">IF(N(C28)&gt;0,MIN(1,N(D28)/C28),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="E30" s="23" t="n">
+      <c r="B30" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="E30" s="24" t="n">
         <f aca="false">SUM(E19:E28)</f>
         <v>225</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="E31" s="29" t="n">
+      <c r="B31" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" s="30" t="n">
         <f aca="false">N(C13)+E30</f>
         <v>475</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="E32" s="23" t="n">
+      <c r="B32" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="E32" s="24" t="n">
         <f aca="false">'T · Track'!E62-E31</f>
         <v>80</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
+      <c r="B33" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4603,260 +4645,260 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="B2" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
+      <c r="B3" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="E5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>175</v>
       </c>
+      <c r="C5" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="C6" s="40" t="n">
+      <c r="B6" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="41" t="n">
         <v>49</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="41" t="n">
         <v>52</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>177</v>
+      <c r="E6" s="21" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="C7" s="40" t="n">
+      <c r="B7" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="41" t="n">
         <v>43</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="41" t="n">
         <v>40</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>179</v>
+      <c r="E7" s="21" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="C8" s="40" t="n">
+      <c r="B8" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="20"/>
+      <c r="E8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="40" t="n">
+      <c r="B9" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>181</v>
+      <c r="E9" s="21" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="C10" s="40" t="n">
+      <c r="B10" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>183</v>
+      <c r="E10" s="21" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C11" s="40" t="n">
+      <c r="B11" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="41" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="41" t="n">
         <v>16</v>
       </c>
-      <c r="E11" s="20" t="s">
-        <v>185</v>
+      <c r="E11" s="21" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="C12" s="40" t="n">
+      <c r="B12" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="20" t="s">
-        <v>187</v>
+      <c r="E12" s="21" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="C13" s="40" t="n">
+      <c r="B13" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D13" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="20" t="s">
-        <v>189</v>
+      <c r="E13" s="21" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="C14" s="40" t="n">
+      <c r="B14" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="40" t="n">
+      <c r="D14" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="E14" s="20"/>
+      <c r="E14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="20"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="20"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="20"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="41" t="s">
-        <v>191</v>
-      </c>
-      <c r="C19" s="47" t="n">
+      <c r="B19" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="48" t="n">
         <f aca="false">SUM(C6:C17)</f>
         <v>145</v>
       </c>
-      <c r="D19" s="47" t="n">
+      <c r="D19" s="48" t="n">
         <f aca="false">SUM(D6:D17)</f>
         <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="C20" s="48" t="n">
+      <c r="B20" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="C20" s="49" t="n">
         <f aca="false">168-C19</f>
         <v>23</v>
       </c>
-      <c r="D20" s="48" t="n">
+      <c r="D20" s="49" t="n">
         <f aca="false">168-D19</f>
         <v>19</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="C22" s="49" t="n">
+      <c r="B22" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="50" t="n">
         <f aca="false">SUMIF(B6:B17,"Family*",D6:D17)-SUMIF(B6:B17,"Family*",C6:C17)</f>
         <v>4</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="C23" s="50" t="n">
+      <c r="B23" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C23" s="51" t="n">
         <f aca="false">C22*52</f>
         <v>208</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
+      <c r="B25" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="41" t="s">
-        <v>196</v>
-      </c>
-      <c r="C28" s="51" t="n">
+      <c r="B28" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="52" t="n">
         <f aca="false">'U · Understand'!C29</f>
         <v>12.0192307692308</v>
       </c>
-      <c r="D28" s="32" t="s">
-        <v>197</v>
-      </c>
-      <c r="E28" s="32"/>
+      <c r="D28" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28" s="33"/>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="C29" s="23" t="n">
+      <c r="B29" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="C29" s="24" t="n">
         <f aca="false">MAX(0,SUMIF(B6:B17,"Paid work*",C6:C17)-SUMIF(B6:B17,"Paid work*",D6:D17))*52*C28</f>
         <v>1875</v>
       </c>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4895,350 +4937,350 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
+      <c r="B2" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
+      <c r="B3" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="E5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="E5" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="F5" s="20" t="s">
         <v>208</v>
       </c>
+      <c r="G5" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="E6" s="40" t="n">
+      <c r="B6" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="G6" s="21" t="n">
+      <c r="F6" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="G6" s="22" t="n">
         <v>150</v>
       </c>
-      <c r="H6" s="52" t="str">
+      <c r="H6" s="53" t="str">
         <f aca="false">IF(N(E6)&gt;0,N(G6)/(E6*52/12),IF(N(G6)&gt;0,"no time logged",""))</f>
         <v>no time logged</v>
       </c>
-      <c r="I6" s="20" t="s">
-        <v>213</v>
+      <c r="I6" s="21" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="E7" s="40" t="n">
+      <c r="B7" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="E7" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="G7" s="21" t="n">
+      <c r="F7" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="G7" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="H7" s="52" t="n">
+      <c r="H7" s="53" t="n">
         <f aca="false">IF(N(E7)&gt;0,N(G7)/(E7*52/12),IF(N(G7)&gt;0,"no time logged",""))</f>
         <v>4.61538461538462</v>
       </c>
-      <c r="I7" s="20" t="s">
-        <v>218</v>
+      <c r="I7" s="21" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="E8" s="40" t="n">
+      <c r="B8" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="21" t="n">
+      <c r="F8" s="21"/>
+      <c r="G8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="52" t="str">
+      <c r="H8" s="53" t="str">
         <f aca="false">IF(N(E8)&gt;0,N(G8)/(E8*52/12),IF(N(G8)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I8" s="20" t="s">
-        <v>222</v>
+      <c r="I8" s="21" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="52" t="str">
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="53" t="str">
         <f aca="false">IF(N(E9)&gt;0,N(G9)/(E9*52/12),IF(N(G9)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I9" s="20"/>
+      <c r="I9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="52" t="str">
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="53" t="str">
         <f aca="false">IF(N(E10)&gt;0,N(G10)/(E10*52/12),IF(N(G10)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I10" s="20"/>
+      <c r="I10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="52" t="str">
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="53" t="str">
         <f aca="false">IF(N(E11)&gt;0,N(G11)/(E11*52/12),IF(N(G11)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I11" s="20"/>
+      <c r="I11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="52" t="str">
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="53" t="str">
         <f aca="false">IF(N(E12)&gt;0,N(G12)/(E12*52/12),IF(N(G12)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I12" s="20"/>
+      <c r="I12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="52" t="str">
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="53" t="str">
         <f aca="false">IF(N(E13)&gt;0,N(G13)/(E13*52/12),IF(N(G13)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I13" s="20"/>
+      <c r="I13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="52" t="str">
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="53" t="str">
         <f aca="false">IF(N(E14)&gt;0,N(G14)/(E14*52/12),IF(N(G14)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I14" s="20"/>
+      <c r="I14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="52" t="str">
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="53" t="str">
         <f aca="false">IF(N(E15)&gt;0,N(G15)/(E15*52/12),IF(N(G15)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I15" s="20"/>
+      <c r="I15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="52" t="str">
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="53" t="str">
         <f aca="false">IF(N(E16)&gt;0,N(G16)/(E16*52/12),IF(N(G16)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I16" s="20"/>
+      <c r="I16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="52" t="str">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="53" t="str">
         <f aca="false">IF(N(E17)&gt;0,N(G17)/(E17*52/12),IF(N(G17)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I17" s="20"/>
+      <c r="I17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="52" t="str">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="53" t="str">
         <f aca="false">IF(N(E18)&gt;0,N(G18)/(E18*52/12),IF(N(G18)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I18" s="20"/>
+      <c r="I18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="52" t="str">
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="53" t="str">
         <f aca="false">IF(N(E19)&gt;0,N(G19)/(E19*52/12),IF(N(G19)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I19" s="20"/>
+      <c r="I19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="52" t="str">
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="53" t="str">
         <f aca="false">IF(N(E20)&gt;0,N(G20)/(E20*52/12),IF(N(G20)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I20" s="20"/>
+      <c r="I20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="52" t="str">
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="53" t="str">
         <f aca="false">IF(N(E21)&gt;0,N(G21)/(E21*52/12),IF(N(G21)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I21" s="20"/>
+      <c r="I21" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="G23" s="29" t="n">
+      <c r="B23" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="G23" s="30" t="n">
         <f aca="false">SUMIF(C6:C21,"&lt;&gt;Career (raise/promotion)",G6:G21)</f>
         <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="41" t="s">
-        <v>224</v>
-      </c>
-      <c r="G24" s="23" t="n">
+      <c r="B24" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="G24" s="24" t="n">
         <f aca="false">SUMIF(C6:C21,"Career (raise/promotion)",G6:G21)</f>
         <v>150</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="E25" s="53" t="n">
+      <c r="B25" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="E25" s="54" t="n">
         <f aca="false">SUM(E6:E21)</f>
         <v>3</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="G26" s="54" t="n">
+      <c r="B26" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="G26" s="55" t="n">
         <f aca="false">IF('T · Track'!E58&gt;0,G23/'T · Track'!E58,0)</f>
         <v>0.0344827586206897</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
+      <c r="B28" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5284,277 +5326,277 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+      <c r="B2" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="B3" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="s">
-        <v>230</v>
+      <c r="B5" s="14" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="55" t="str">
+      <c r="B6" s="56" t="str">
         <f aca="false">INDEX(Lists!$F$1:$F$7,C9+1)</f>
         <v>Level 1 · Stable</v>
       </c>
-      <c r="C6" s="55"/>
-      <c r="E6" s="56" t="str">
+      <c r="C6" s="56"/>
+      <c r="E6" s="57" t="str">
         <f aca="false">CHOOSE(C9+1,"Next step: more goes out than comes in. Use R · Reclaim and cut wants until KEEP is at least €0.","Next step: build a starter buffer of one month of needs before anything else.","Next step: clear consumer debt, highest interest first (Priority 1 on U · Understand).","Next step: grow the buffer into your full emergency fund on S · Save.","Next step: you are secure. Learn long-term investing basics and start ONE income stream.","Next step: extra income covers 25%+ of needs. Keep investing; decide what time you want back.","You have choices. Extra income covers your baseline. Decide on your terms how much you want to work.")</f>
         <v>Next step: build a starter buffer of one month of needs before anything else.</v>
       </c>
-      <c r="F6" s="56"/>
+      <c r="F6" s="57"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="C9" s="57" t="n">
+      <c r="B9" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" s="58" t="n">
         <f aca="false">IF(C14&lt;0,0,IF(C22&lt;C13,1,IF(C20&gt;0,2,IF(C22&lt;C23,3,IF(C25&lt;0.25*C13,4,IF(C25&lt;C13,5,6))))))</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>233</v>
+      <c r="B11" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="C12" s="58" t="n">
+      <c r="B12" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" s="59" t="n">
         <f aca="false">'T · Track'!E13</f>
         <v>2560</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="F12" s="59" t="n">
+      <c r="E12" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="F12" s="60" t="n">
         <f aca="false">'U · Understand'!C29</f>
         <v>12.0192307692308</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="C13" s="60" t="n">
+      <c r="B13" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="61" t="n">
         <f aca="false">'T · Track'!E58</f>
         <v>1740</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="F13" s="61" t="n">
+      <c r="E13" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="62" t="n">
         <f aca="false">'U · Understand'!C31</f>
         <v>252.403846153846</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="C14" s="61" t="n">
+      <c r="B14" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="62" t="n">
         <f aca="false">'T · Track'!E62</f>
         <v>555</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="F14" s="62" t="n">
+      <c r="E14" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="F14" s="63" t="n">
         <f aca="false">'Income Streams'!E25</f>
         <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" s="63" t="n">
+      <c r="B15" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="64" t="n">
         <f aca="false">'T · Track'!E63</f>
         <v>0.216796875</v>
       </c>
-      <c r="E15" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="F15" s="64" t="n">
+      <c r="E15" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="F15" s="65" t="n">
         <f aca="false">'Income Streams'!G26</f>
         <v>0.0344827586206897</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="65" t="n">
+      <c r="B16" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="66" t="n">
         <f aca="false">'T · Track'!E59</f>
         <v>265</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="F16" s="66" t="n">
+      <c r="E16" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="F16" s="67" t="n">
         <f aca="false">'T · Time'!C22</f>
         <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="C17" s="61" t="n">
+      <c r="B17" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C17" s="62" t="n">
         <f aca="false">'R · Reclaim'!F32</f>
         <v>48</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="F17" s="58" t="n">
+      <c r="E17" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="F17" s="59" t="n">
         <f aca="false">'S · Save'!E32</f>
         <v>80</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="C18" s="61" t="n">
+      <c r="B18" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" s="62" t="n">
         <f aca="false">'R · Reclaim'!F33</f>
         <v>576</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="F18" s="61" t="n">
+      <c r="E18" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F18" s="62" t="n">
         <f aca="false">'Income Streams'!G24</f>
         <v>150</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="18" t="s">
-        <v>245</v>
+      <c r="B19" s="19" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="C20" s="65" t="n">
+      <c r="B20" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C20" s="66" t="n">
         <f aca="false">'U · Understand'!C17</f>
         <v>1500</v>
       </c>
-      <c r="E20" s="67" t="s">
-        <v>247</v>
+      <c r="E20" s="68" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="65" t="n">
+      <c r="B21" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="66" t="n">
         <f aca="false">'U · Understand'!C19</f>
         <v>298.5</v>
       </c>
-      <c r="E21" s="68" t="s">
-        <v>248</v>
-      </c>
-      <c r="F21" s="68"/>
+      <c r="E21" s="69" t="s">
+        <v>251</v>
+      </c>
+      <c r="F21" s="69"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="C22" s="61" t="n">
+      <c r="B22" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" s="62" t="n">
         <f aca="false">'S · Save'!C11</f>
         <v>1200</v>
       </c>
-      <c r="E22" s="68" t="s">
-        <v>250</v>
-      </c>
-      <c r="F22" s="68"/>
+      <c r="E22" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="F22" s="69"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="C23" s="60" t="n">
+      <c r="B23" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C23" s="61" t="n">
         <f aca="false">'S · Save'!C10</f>
         <v>5220</v>
       </c>
-      <c r="E23" s="68" t="s">
-        <v>252</v>
-      </c>
-      <c r="F23" s="68"/>
+      <c r="E23" s="69" t="s">
+        <v>255</v>
+      </c>
+      <c r="F23" s="69"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="C24" s="63" t="n">
+      <c r="B24" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C24" s="64" t="n">
         <f aca="false">'S · Save'!C12</f>
         <v>0.229885057471264</v>
       </c>
-      <c r="E24" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="F24" s="68"/>
+      <c r="E24" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="F24" s="69"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="C25" s="61" t="n">
+      <c r="B25" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C25" s="62" t="n">
         <f aca="false">'Income Streams'!G23</f>
         <v>60</v>
       </c>
-      <c r="E25" s="68" t="s">
-        <v>256</v>
-      </c>
-      <c r="F25" s="68"/>
+      <c r="E25" s="69" t="s">
+        <v>259</v>
+      </c>
+      <c r="F25" s="69"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E26" s="68" t="s">
-        <v>257</v>
-      </c>
-      <c r="F26" s="68"/>
+      <c r="E26" s="69" t="s">
+        <v>260</v>
+      </c>
+      <c r="F26" s="69"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E27" s="68" t="s">
-        <v>258</v>
-      </c>
-      <c r="F27" s="68"/>
+      <c r="E27" s="69" t="s">
+        <v>261</v>
+      </c>
+      <c r="F27" s="69"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="69" t="s">
-        <v>259</v>
+      <c r="B28" s="70" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="70" t="s">
-        <v>260</v>
+      <c r="B29" s="71" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -82,7 +82,7 @@
     <t xml:space="preserve">You work hard for your money. But is it creating the life you're working so hard for?</t>
   </si>
   <si>
-    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and alongside my 9–5 I support my mum, who receives care at home after her cerebral haemorrhage. Balancing both is demanding, so I know how little time is left at the end of the day. Everything here comes from my own experience: I paid off €20,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I live it every week.</t>
+    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and alongside my 9–5 I support my mum, who receives care at home after her cerebral haemorrhage. Balancing both is demanding, so I know how little time is left at the end of the day. Everything here comes from my own experience: I paid off €20,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I've experienced it myself.</t>
   </si>
   <si>
     <t xml:space="preserve">You have a demanding career, bills to pay and people who depend on you. You earn a respectable income. Yet despite everything you do, you don't always feel as financially secure or independent as you thought you would.</t>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">How do I build a financially secure future without missing out on the people and moments that matter most today?</t>
   </si>
   <si>
-    <t xml:space="preserve">I know that feeling. I started as a flight attendant working toward becoming a pilot, until COVID changed those plans. I rebuilt my path in cybersecurity consulting. My income grew, but financial security didn't automatically follow. I paid off €20,000 of debt not by first earning more, but by understanding my finances and making deliberate changes.</t>
+    <t xml:space="preserve">I know that feeling. I started as a flight attendant working toward becoming a pilot, until COVID changed those plans. I rebuilt my path in cybersecurity consulting. My income grew, but financial security didn't automatically follow. In my 20s I took on loans for my study fees, made wrong financial decisions and even fell for an online scam. I paid off €20,000 of debt not by first earning more, but by understanding my finances and making deliberate changes. Now in my 30s, this is what I wish someone had told me in my 20s.</t>
   </si>
   <si>
     <t xml:space="preserve">WHY I REALLY BUILT THIS</t>
@@ -1922,7 +1922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">How do I build a financially secure future without missing out on the people and moments that matter most today?</t>
   </si>
   <si>
-    <t xml:space="preserve">I know that feeling. I started as a flight attendant working toward becoming a pilot, until COVID changed those plans. I rebuilt my path in cybersecurity consulting. My income grew, but financial security didn't automatically follow. In my 20s I took on loans for my study fees, made wrong financial decisions and even fell for an online scam. I paid off €20,000 of debt not by first earning more, but by understanding my finances and making deliberate changes. Now in my 30s, this is what I wish someone had told me in my 20s.</t>
+    <t xml:space="preserve">I know that feeling. I started as a flight attendant working toward becoming a pilot, until COVID changed those plans. I rebuilt my path in cybersecurity consulting. My income grew, but financial security didn't automatically follow. In my 20s I took on loans for my study fees, made wrong financial decisions and even fell for an online scam: I was heavily into trading without knowing much about it. My rule since then: only invest in what you understand. I paid off €20,000 of debt not by first earning more, but by understanding my finances and making deliberate changes. Now in my 30s, this is what I wish someone had told me in my 20s.</t>
   </si>
   <si>
     <t xml:space="preserve">WHY I REALLY BUILT THIS</t>
@@ -1922,7 +1922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="304">
   <si>
     <t xml:space="preserve">Hey, I'm Liliane.</t>
   </si>
@@ -149,6 +149,27 @@
   </si>
   <si>
     <t xml:space="preserve">Knowing your numbers is the beginning, not the goal. TRUST is the foundation for debt freedom, wealth building and additional income.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WEALTH STARTS WITH YOUR MINDSET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming wealthy starts with how you think about money and with understanding the laws of money. Money management is a skill you learn, not a talent you're born with.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · Spend less than you earn. The gap is where all wealth begins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 · Pay yourself first. Your future gets paid on payday, before bills and wants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 · Protect what you have. A safety net and no expensive debt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 · Make your money work for you. Only invest in what you understand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 · Give it time. Compound growth rewards patience more than luck.</t>
   </si>
   <si>
     <t xml:space="preserve">YOUR NEXT STEP</t>
@@ -1889,7 +1910,7 @@
     <tabColor rgb="FF9E1B5E"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B38"/>
+  <dimension ref="B2:B46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2032,19 +2053,54 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="9" t="s">
+    <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="10" t="s">
+    <row r="35" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="11" t="s">
+    <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="4" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2079,7 +2135,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -2094,7 +2150,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -2109,42 +2165,42 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="20" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="K5" s="20" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="21" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>2500</v>
@@ -2177,12 +2233,12 @@
         <v>Level 1 · Stable</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C7" s="22" t="n">
         <v>2560</v>
@@ -2215,7 +2271,7 @@
         <v>Level 1 · Stable</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2463,160 +2519,160 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -2647,51 +2703,51 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C3" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="14" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="15" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="15" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="15" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2700,23 +2756,23 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="14" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="15" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="15" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2725,31 +2781,31 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="14" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="17" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="15" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2759,7 +2815,7 @@
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="15"/>
       <c r="C20" s="16" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2796,7 +2852,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -2805,7 +2861,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -2814,26 +2870,26 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="20" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E7" s="22" t="n">
         <v>2500</v>
@@ -2841,10 +2897,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E8" s="23" t="n">
         <f aca="false">'Income Streams'!G23</f>
@@ -2853,10 +2909,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E9" s="22" t="n">
         <v>0</v>
@@ -2879,7 +2935,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="15" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E13" s="24" t="n">
         <f aca="false">SUM(E7:E12)</f>
@@ -2888,52 +2944,52 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="19" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="21" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E17" s="22" t="n">
         <v>900</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E18" s="22" t="n">
         <v>140</v>
@@ -2942,13 +2998,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E19" s="22" t="n">
         <v>320</v>
@@ -2957,13 +3013,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="21" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E20" s="22" t="n">
         <v>90</v>
@@ -2972,13 +3028,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>73</v>
       </c>
       <c r="E21" s="22" t="n">
         <v>80</v>
@@ -2987,13 +3043,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="21" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E22" s="22" t="n">
         <v>150</v>
@@ -3002,13 +3058,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="21" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E23" s="22" t="n">
         <v>60</v>
@@ -3017,13 +3073,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="21" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E24" s="22" t="n">
         <v>45</v>
@@ -3032,13 +3088,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="21" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E25" s="22" t="n">
         <v>120</v>
@@ -3047,13 +3103,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E26" s="22" t="n">
         <v>100</v>
@@ -3272,7 +3328,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="15" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E58" s="24" t="n">
         <f aca="false">SUMIF(D17:D56,"Need",E17:E56)</f>
@@ -3281,7 +3337,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="15" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E59" s="24" t="n">
         <f aca="false">SUMIF(D17:D56,"Want",E17:E56)</f>
@@ -3290,7 +3346,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="25" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E60" s="26" t="n">
         <f aca="false">SUMIF(C17:C56,"Caregiving",E17:E56)</f>
@@ -3299,7 +3355,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="27" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E61" s="28" t="n">
         <f aca="false">SUM(E17:E56)-E58-E59</f>
@@ -3308,7 +3364,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="29" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E62" s="30" t="n">
         <f aca="false">E13-E58-E59</f>
@@ -3317,7 +3373,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="29" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E63" s="31" t="n">
         <f aca="false">IF(E13&gt;0,E62/E13,0)</f>
@@ -3369,7 +3425,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -3379,7 +3435,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -3389,33 +3445,33 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="20" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="21" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>13</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E6" s="22" t="n">
         <v>0</v>
@@ -3425,18 +3481,18 @@
         <v>13</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C7" s="22" t="n">
         <v>35</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E7" s="22" t="n">
         <v>15</v>
@@ -3446,18 +3502,18 @@
         <v>20</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C8" s="22" t="n">
         <v>40</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E8" s="22" t="n">
         <v>25</v>
@@ -3467,18 +3523,18 @@
         <v>15</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C9" s="22" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E9" s="22" t="n">
         <v>3</v>
@@ -3722,7 +3778,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="15" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F32" s="30" t="n">
         <f aca="false">SUM(F6:F30)</f>
@@ -3731,7 +3787,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="15" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F33" s="30" t="n">
         <f aca="false">F32*12</f>
@@ -3740,7 +3796,7 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="33" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C35" s="33"/>
       <c r="D35" s="33"/>
@@ -3792,7 +3848,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -3804,7 +3860,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -3816,33 +3872,33 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="20" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="21" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>1500</v>
@@ -3871,7 +3927,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C7" s="22" t="n">
         <v>0</v>
@@ -4052,14 +4108,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="15" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C17" s="38" t="n">
         <f aca="false">SUM(C6:C15)</f>
         <v>1500</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E17" s="33"/>
       <c r="F17" s="33"/>
@@ -4069,7 +4125,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C18" s="39" t="n">
         <f aca="false">SUM(G6:G15)</f>
@@ -4084,7 +4140,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="15" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C19" s="38" t="n">
         <f aca="false">C18*12</f>
@@ -4099,27 +4155,27 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="19" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="20" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="16" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C24" s="40" t="n">
         <f aca="false">'T · Track'!E7</f>
         <v>2500</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E24" s="33"/>
       <c r="F24" s="33"/>
@@ -4129,7 +4185,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="16" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C25" s="41" t="n">
         <v>39</v>
@@ -4143,7 +4199,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="16" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C26" s="41" t="n">
         <v>4</v>
@@ -4157,7 +4213,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="16" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C27" s="41" t="n">
         <v>5</v>
@@ -4171,7 +4227,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="42" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C28" s="43" t="n">
         <f aca="false">(N(C25)+N(C26)+N(C27))*52/12</f>
@@ -4186,14 +4242,14 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C29" s="44" t="n">
         <f aca="false">IF(C28&gt;0,C24/C28,0)</f>
         <v>12.0192307692308</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E29" s="33"/>
       <c r="F29" s="33"/>
@@ -4203,7 +4259,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="16" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C30" s="45" t="n">
         <v>21</v>
@@ -4217,7 +4273,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="29" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C31" s="30" t="n">
         <f aca="false">C29*N(C30)</f>
@@ -4268,7 +4324,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -4278,7 +4334,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -4288,27 +4344,27 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="20" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="16" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C7" s="40" t="n">
         <f aca="false">'T · Track'!E58</f>
         <v>1740</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E7" s="33"/>
       <c r="F7" s="33"/>
@@ -4316,7 +4372,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="16" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C8" s="45" t="n">
         <v>3</v>
@@ -4328,7 +4384,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="42" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C9" s="46" t="n">
         <f aca="false">C7</f>
@@ -4341,7 +4397,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="42" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C10" s="24" t="n">
         <f aca="false">C7*N(C8)</f>
@@ -4354,7 +4410,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="16" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>1200</v>
@@ -4362,7 +4418,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="29" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C12" s="31" t="n">
         <f aca="false">IF(C10&gt;0,MIN(1,N(C11)/C10),0)</f>
@@ -4371,7 +4427,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="16" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>250</v>
@@ -4379,7 +4435,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="42" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C14" s="36" t="n">
         <f aca="false">IF(N(C11)&gt;=C10,"Done ✓",IF(N(C13)&gt;0,ROUNDUP((C10-N(C11))/C13,0),"Add a transfer"))</f>
@@ -4388,32 +4444,32 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="19" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="20" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F18" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="G18" s="20" t="s">
         <v>165</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C19" s="22" t="n">
         <v>1500</v>
@@ -4435,7 +4491,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="21" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C20" s="22" t="n">
         <v>600</v>
@@ -4457,7 +4513,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="21" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C21" s="22" t="n">
         <v>1800</v>
@@ -4577,7 +4633,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="42" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="E30" s="24" t="n">
         <f aca="false">SUM(E19:E28)</f>
@@ -4586,7 +4642,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="29" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E31" s="30" t="n">
         <f aca="false">N(C13)+E30</f>
@@ -4595,7 +4651,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="15" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E32" s="24" t="n">
         <f aca="false">'T · Track'!E62-E31</f>
@@ -4604,7 +4660,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="33" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C33" s="33"/>
       <c r="D33" s="33"/>
@@ -4646,7 +4702,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -4654,7 +4710,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -4662,21 +4718,21 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="20" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="21" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C6" s="41" t="n">
         <v>49</v>
@@ -4685,12 +4741,12 @@
         <v>52</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C7" s="41" t="n">
         <v>43</v>
@@ -4699,12 +4755,12 @@
         <v>40</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C8" s="41" t="n">
         <v>5</v>
@@ -4716,7 +4772,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C9" s="41" t="n">
         <v>10</v>
@@ -4725,12 +4781,12 @@
         <v>10</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="21" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C10" s="41" t="n">
         <v>10</v>
@@ -4739,12 +4795,12 @@
         <v>8</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="21" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C11" s="41" t="n">
         <v>12</v>
@@ -4753,12 +4809,12 @@
         <v>16</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C12" s="41" t="n">
         <v>3</v>
@@ -4767,12 +4823,12 @@
         <v>4</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="21" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C13" s="41" t="n">
         <v>3</v>
@@ -4781,12 +4837,12 @@
         <v>4</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="21" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C14" s="41" t="n">
         <v>10</v>
@@ -4816,7 +4872,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="42" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C19" s="48" t="n">
         <f aca="false">SUM(C6:C17)</f>
@@ -4829,7 +4885,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="29" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C20" s="49" t="n">
         <f aca="false">168-C19</f>
@@ -4842,7 +4898,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="18" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C22" s="50" t="n">
         <f aca="false">SUMIF(B6:B17,"Family*",D6:D17)-SUMIF(B6:B17,"Family*",C6:C17)</f>
@@ -4851,7 +4907,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="18" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C23" s="51" t="n">
         <f aca="false">C22*52</f>
@@ -4860,7 +4916,7 @@
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="33" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
@@ -4874,20 +4930,20 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="42" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C28" s="52" t="n">
         <f aca="false">'U · Understand'!C29</f>
         <v>12.0192307692308</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E28" s="33"/>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="42" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C29" s="24" t="n">
         <f aca="false">MAX(0,SUMIF(B6:B17,"Paid work*",C6:C17)-SUMIF(B6:B17,"Paid work*",D6:D17))*52*C28</f>
@@ -4938,7 +4994,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -4950,7 +5006,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -4962,45 +5018,45 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="20" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="21" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E6" s="41" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="G6" s="22" t="n">
         <v>150</v>
@@ -5010,24 +5066,24 @@
         <v>no time logged</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E7" s="41" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="G7" s="22" t="n">
         <v>60</v>
@@ -5037,18 +5093,18 @@
         <v>4.61538461538462</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E8" s="41" t="n">
         <v>0</v>
@@ -5062,7 +5118,7 @@
         <v/>
       </c>
       <c r="I8" s="21" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5236,7 +5292,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="29" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G23" s="30" t="n">
         <f aca="false">SUMIF(C6:C21,"&lt;&gt;Career (raise/promotion)",G6:G21)</f>
@@ -5245,7 +5301,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="42" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="G24" s="24" t="n">
         <f aca="false">SUMIF(C6:C21,"Career (raise/promotion)",G6:G21)</f>
@@ -5254,7 +5310,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="42" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E25" s="54" t="n">
         <f aca="false">SUM(E6:E21)</f>
@@ -5263,7 +5319,7 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="18" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="G26" s="55" t="n">
         <f aca="false">IF('T · Track'!E58&gt;0,G23/'T · Track'!E58,0)</f>
@@ -5272,7 +5328,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="33" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C28" s="33"/>
       <c r="D28" s="33"/>
@@ -5327,7 +5383,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="12" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -5336,7 +5392,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -5345,7 +5401,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="14" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5368,7 +5424,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="16" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C9" s="58" t="n">
         <f aca="false">IF(C14&lt;0,0,IF(C22&lt;C13,1,IF(C20&gt;0,2,IF(C22&lt;C23,3,IF(C25&lt;0.25*C13,4,IF(C25&lt;C13,5,6))))))</f>
@@ -5377,22 +5433,22 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="19" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="16" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C12" s="59" t="n">
         <f aca="false">'T · Track'!E13</f>
         <v>2560</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="F12" s="60" t="n">
         <f aca="false">'U · Understand'!C29</f>
@@ -5401,14 +5457,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="16" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C13" s="61" t="n">
         <f aca="false">'T · Track'!E58</f>
         <v>1740</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F13" s="62" t="n">
         <f aca="false">'U · Understand'!C31</f>
@@ -5417,14 +5473,14 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="16" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C14" s="62" t="n">
         <f aca="false">'T · Track'!E62</f>
         <v>555</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F14" s="63" t="n">
         <f aca="false">'Income Streams'!E25</f>
@@ -5433,14 +5489,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="16" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C15" s="64" t="n">
         <f aca="false">'T · Track'!E63</f>
         <v>0.216796875</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F15" s="65" t="n">
         <f aca="false">'Income Streams'!G26</f>
@@ -5449,14 +5505,14 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="16" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C16" s="66" t="n">
         <f aca="false">'T · Track'!E59</f>
         <v>265</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F16" s="67" t="n">
         <f aca="false">'T · Time'!C22</f>
@@ -5465,14 +5521,14 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="16" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C17" s="62" t="n">
         <f aca="false">'R · Reclaim'!F32</f>
         <v>48</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="F17" s="59" t="n">
         <f aca="false">'S · Save'!E32</f>
@@ -5481,14 +5537,14 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="16" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C18" s="62" t="n">
         <f aca="false">'R · Reclaim'!F33</f>
         <v>576</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="F18" s="62" t="n">
         <f aca="false">'Income Streams'!G24</f>
@@ -5497,106 +5553,106 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="19" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="16" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C20" s="66" t="n">
         <f aca="false">'U · Understand'!C17</f>
         <v>1500</v>
       </c>
       <c r="E20" s="68" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="16" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C21" s="66" t="n">
         <f aca="false">'U · Understand'!C19</f>
         <v>298.5</v>
       </c>
       <c r="E21" s="69" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="F21" s="69"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="16" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C22" s="62" t="n">
         <f aca="false">'S · Save'!C11</f>
         <v>1200</v>
       </c>
       <c r="E22" s="69" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="F22" s="69"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="16" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C23" s="61" t="n">
         <f aca="false">'S · Save'!C10</f>
         <v>5220</v>
       </c>
       <c r="E23" s="69" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="F23" s="69"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="16" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C24" s="64" t="n">
         <f aca="false">'S · Save'!C12</f>
         <v>0.229885057471264</v>
       </c>
       <c r="E24" s="69" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F24" s="69"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="16" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C25" s="62" t="n">
         <f aca="false">'Income Streams'!G23</f>
         <v>60</v>
       </c>
       <c r="E25" s="69" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="F25" s="69"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E26" s="69" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="F26" s="69"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E27" s="69" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="F27" s="69"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="70" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="71" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -82,7 +82,7 @@
     <t xml:space="preserve">You work hard for your money. But is it creating the life you're working so hard for?</t>
   </si>
   <si>
-    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and alongside my 9–5 I support my mum, who receives care at home after her cerebral haemorrhage. Balancing both is demanding, so I know how little time is left at the end of the day. Everything here comes from my own experience: I paid off €20,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I've experienced it myself.</t>
+    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and alongside my 9–5 I support my mum, who receives care at home after her cerebral haemorrhage. Balancing both is demanding, so I know how little time is left at the end of the day. Everything here comes from my own experience: I paid off €30,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I've experienced it myself.</t>
   </si>
   <si>
     <t xml:space="preserve">You have a demanding career, bills to pay and people who depend on you. You earn a respectable income. Yet despite everything you do, you don't always feel as financially secure or independent as you thought you would.</t>
@@ -91,7 +91,7 @@
     <t xml:space="preserve">How do I build a financially secure future without missing out on the people and moments that matter most today?</t>
   </si>
   <si>
-    <t xml:space="preserve">I know that feeling. I started as a flight attendant working toward becoming a pilot, until COVID changed those plans. I rebuilt my path in cybersecurity consulting. My income grew, but financial security didn't automatically follow. In my 20s I took on loans for my study fees, made wrong financial decisions and even fell for an online scam: I was heavily into trading without knowing much about it. My rule since then: only invest in what you understand. I paid off €20,000 of debt not by first earning more, but by understanding my finances and making deliberate changes. Now in my 30s, this is what I wish someone had told me in my 20s.</t>
+    <t xml:space="preserve">I know that feeling. I started as a flight attendant working toward becoming a pilot, until COVID changed those plans. I rebuilt my path in cybersecurity consulting. My income grew, but financial security didn't automatically follow. In my 20s I took on loans for my study fees, made wrong financial decisions and even fell for an online scam: I was heavily into trading without knowing much about it. My rule since then: only invest in what you understand. I paid off €30,000 of debt not by first earning more, but by understanding my finances and making deliberate changes. Now in my 30s, this is what I wish someone had told me in my 20s.</t>
   </si>
   <si>
     <t xml:space="preserve">WHY I REALLY BUILT THIS</t>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -97,7 +97,7 @@
     <t xml:space="preserve">WHY I REALLY BUILT THIS</t>
   </si>
   <si>
-    <t xml:space="preserve">My mum is 83. When she had her cerebral haemorrhage, I realised how valuable time really is, and how little of it I had left after work. I want to spend as much time with her as I possibly can. Not someday, but now.</t>
+    <t xml:space="preserve">My mum is 83. When she had her cerebral haemorrhage, I realised how valuable time really is, and how little of it I had left. For years I worked long hours and stayed late almost every single day, because I believed climbing the corporate ladder was what success meant. But true success is realising what truly matters in life, and then taking the steps, one by one, that lead you there. We only get this one life. I want to spend as much time with her as I possibly can. Not someday, but now.</t>
   </si>
   <si>
     <t xml:space="preserve">Every plan I found told me to quit my job or hustle harder. None were made for someone with a demanding career and a parent who needs them. I wished I'd had a clear, honest plan for the few hours I actually had. So I built it for myself. You shouldn't need a wake-up call to start.</t>
@@ -1953,7 +1953,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
         <v>7</v>
       </c>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -100,7 +100,7 @@
     <t xml:space="preserve">My mum is 83. When she had her cerebral haemorrhage, I realised how valuable time really is, and how little of it I had left. For years I worked long hours and stayed late almost every single day, because I believed climbing the corporate ladder was what success meant. But true success is realising what truly matters in life, and then taking the steps, one by one, that lead you there. We only get this one life. I want to spend as much time with her as I possibly can. Not someday, but now.</t>
   </si>
   <si>
-    <t xml:space="preserve">Every plan I found told me to quit my job or hustle harder. None were made for someone with a demanding career and a parent who needs them. I wished I'd had a clear, honest plan for the few hours I actually had. So I built it for myself. You shouldn't need a wake-up call to start.</t>
+    <t xml:space="preserve">Every plan I found told me to quit my job, hustle harder or get rich fast. That's unrealistic unless you're willing to risk your financial security, and when people depend on you, that's not a risk worth taking. None were made for someone with a demanding career and a parent who needs them. I wished I'd had a clear, honest plan for the few hours I actually had. So I built it for myself. You shouldn't need a wake-up call to start.</t>
   </si>
   <si>
     <t xml:space="preserve">That's why I created the TRUST Sheet. No judgment. No unrealistic promises. No complicated jargon. Just a practical starting point for making your money work toward the life you actually want.</t>
@@ -1958,7 +1958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
         <v>8</v>
       </c>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -100,7 +100,7 @@
     <t xml:space="preserve">My mum is 83. When she had her cerebral haemorrhage, I realised how valuable time really is, and how little of it I had left. For years I worked long hours and stayed late almost every single day, because I believed climbing the corporate ladder was what success meant. But true success is realising what truly matters in life, and then taking the steps, one by one, that lead you there. We only get this one life. I want to spend as much time with her as I possibly can. Not someday, but now.</t>
   </si>
   <si>
-    <t xml:space="preserve">Every plan I found told me to quit my job, hustle harder or get rich fast. That's unrealistic unless you're willing to risk your financial security, and when people depend on you, that's not a risk worth taking. None were made for someone with a demanding career and a parent who needs them. I wished I'd had a clear, honest plan for the few hours I actually had. So I built it for myself. You shouldn't need a wake-up call to start.</t>
+    <t xml:space="preserve">Most of the financial advice out there told me to quit my job, hustle harder or get rich fast. That's unrealistic unless you're willing to risk your financial security, and when people depend on you, that's not a risk worth taking. None were made for someone with a demanding career and a parent who needs them. I wished I'd had a clear, honest plan for the few hours I actually had. So I built it for myself. You shouldn't need a wake-up call to start.</t>
   </si>
   <si>
     <t xml:space="preserve">That's why I created the TRUST Sheet. No judgment. No unrealistic promises. No complicated jargon. Just a practical starting point for making your money work toward the life you actually want.</t>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -100,7 +100,7 @@
     <t xml:space="preserve">My mum is 83. When she had her cerebral haemorrhage, I realised how valuable time really is, and how little of it I had left. For years I worked long hours and stayed late almost every single day, because I believed climbing the corporate ladder was what success meant. But true success is realising what truly matters in life, and then taking the steps, one by one, that lead you there. We only get this one life. I want to spend as much time with her as I possibly can. Not someday, but now.</t>
   </si>
   <si>
-    <t xml:space="preserve">Most of the financial advice out there told me to quit my job, hustle harder or get rich fast. That's unrealistic unless you're willing to risk your financial security, and when people depend on you, that's not a risk worth taking. None were made for someone with a demanding career and a parent who needs them. I wished I'd had a clear, honest plan for the few hours I actually had. So I built it for myself. You shouldn't need a wake-up call to start.</t>
+    <t xml:space="preserve">Most of the financial advice out there told me to quit my job, hustle harder or get rich fast. That's unrealistic unless you're willing to risk your financial security, and when people depend on you, that's not a risk worth taking. None were made for someone with a demanding career and a mum who needs them. I wished I'd had a clear, honest plan for the few hours I actually had. So I built it for myself. You shouldn't need a wake-up call to start.</t>
   </si>
   <si>
     <t xml:space="preserve">That's why I created the TRUST Sheet. No judgment. No unrealistic promises. No complicated jargon. Just a practical starting point for making your money work toward the life you actually want.</t>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -100,7 +100,7 @@
     <t xml:space="preserve">My mum is 83. When she had her cerebral haemorrhage, I realised how valuable time really is, and how little of it I had left. For years I worked long hours and stayed late almost every single day, because I believed climbing the corporate ladder was what success meant. But true success is realising what truly matters in life, and then taking the steps, one by one, that lead you there. We only get this one life. I want to spend as much time with her as I possibly can. Not someday, but now.</t>
   </si>
   <si>
-    <t xml:space="preserve">Most of the financial advice out there told me to quit my job, hustle harder or get rich fast. That's unrealistic unless you're willing to risk your financial security, and when people depend on you, that's not a risk worth taking. None were made for someone with a demanding career and a mum who needs them. I wished I'd had a clear, honest plan for the few hours I actually had. So I built it for myself. You shouldn't need a wake-up call to start.</t>
+    <t xml:space="preserve">Most of the financial advice out there told me to quit my job, hustle harder or get rich fast. That's unrealistic unless you're willing to risk your financial security, and when people depend on you, that's not a risk worth taking. None were made for someone with a demanding career and a mum who needs them. I wished I'd had a clear, honest plan for the few hours I actually had left, when I wasn't already exhausted from work and every other responsibility around me. So I built it for myself. You shouldn't need a wake-up call to start.</t>
   </si>
   <si>
     <t xml:space="preserve">That's why I created the TRUST Sheet. No judgment. No unrealistic promises. No complicated jargon. Just a practical starting point for making your money work toward the life you actually want.</t>
@@ -1958,7 +1958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
         <v>8</v>
       </c>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -100,7 +100,7 @@
     <t xml:space="preserve">My mum is 83. When she had her cerebral haemorrhage, I realised how valuable time really is, and how little of it I had left. For years I worked long hours and stayed late almost every single day, because I believed climbing the corporate ladder was what success meant. But true success is realising what truly matters in life, and then taking the steps, one by one, that lead you there. We only get this one life. I want to spend as much time with her as I possibly can. Not someday, but now.</t>
   </si>
   <si>
-    <t xml:space="preserve">Most of the financial advice out there told me to quit my job, hustle harder or get rich fast. That's unrealistic unless you're willing to risk your financial security, and when people depend on you, that's not a risk worth taking. None were made for someone with a demanding career and a mum who needs them. I wished I'd had a clear, honest plan for the few hours I actually had left, when I wasn't already exhausted from work and every other responsibility around me. So I built it for myself. You shouldn't need a wake-up call to start.</t>
+    <t xml:space="preserve">Most of the financial advice out there told me to quit my job, hustle harder or get rich fast. That's unrealistic unless you're willing to risk your financial security, and when people depend on you, that's not a risk worth taking. None were made for someone with a demanding career and a mum who needs them. I wish I'd had a clear, honest plan for the few hours I actually had left, when I wasn't already exhausted from work and every other responsibility around me. So I decided to build it for myself, step by step. You shouldn't need a wake-up call to start. Begin before yours comes, or before it's too late.</t>
   </si>
   <si>
     <t xml:space="preserve">That's why I created the TRUST Sheet. No judgment. No unrealistic promises. No complicated jargon. Just a practical starting point for making your money work toward the life you actually want.</t>

--- a/icyber/TRUST-Tracker-Freedom-Edition.xlsx
+++ b/icyber/TRUST-Tracker-Freedom-Edition.xlsx
@@ -82,7 +82,7 @@
     <t xml:space="preserve">You work hard for your money. But is it creating the life you're working so hard for?</t>
   </si>
   <si>
-    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm. I work a demanding job, and alongside my 9–5 I support my mum, who receives care at home after her cerebral haemorrhage. Balancing both is demanding, so I know how little time is left at the end of the day. Everything here comes from my own experience: I paid off €30,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I've experienced it myself.</t>
+    <t xml:space="preserve">I'm a full-time cybersecurity consultant at a Big Four firm, working in the financial sector. I work a demanding job, and alongside my 9–5 I support my mum, who receives care at home after her cerebral haemorrhage. Balancing both is demanding, so I know how little time is left at the end of the day. Everything here comes from my own experience: I paid off €30,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I've experienced it myself.</t>
   </si>
   <si>
     <t xml:space="preserve">You have a demanding career, bills to pay and people who depend on you. You earn a respectable income. Yet despite everything you do, you don't always feel as financially secure or independent as you thought you would.</t>
